--- a/Models/Лошади/results/Лошади - Результаты прогнозов ХВ.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[1591.57, 1062.7, 1010.87]</t>
+          <t>[931.67, 1304.68, 981.26]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[1655.9, 915.95, 1074.61]</t>
+          <t>[995.56, 1304.96, 1013.53]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>99.55961298808451</v>
+        <v>41.3262509800898</v>
       </c>
       <c r="G2" t="n">
-        <v>91.60748739692617</v>
+        <v>32.14749613921109</v>
       </c>
       <c r="H2" t="n">
-        <v>8.612694569890579</v>
+        <v>3.207696411767892</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[1067.12, 1015.0, 897.83]</t>
+          <t>[1311.76, 986.56, 2054.63]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[915.95, 1074.61, 852.53]</t>
+          <t>[1304.96, 1013.53, 2212.19]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97.39753693830465</v>
+        <v>92.37526946507239</v>
       </c>
       <c r="G3" t="n">
-        <v>85.36153147681466</v>
+        <v>63.77982679921013</v>
       </c>
       <c r="H3" t="n">
-        <v>9.121833087039926</v>
+        <v>3.435056215363165</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[1000.35, 883.41, 1162.72]</t>
+          <t>[986.05, 2053.6, 1821.92]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[1074.61, 852.53, 1126.55]</t>
+          <t>[1013.53, 2212.19, 1876.09]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50.91436289749385</v>
+        <v>98.04625449483787</v>
       </c>
       <c r="G4" t="n">
-        <v>47.10452701713359</v>
+        <v>80.07748855021289</v>
       </c>
       <c r="H4" t="n">
-        <v>4.581172226052789</v>
+        <v>4.255725856390604</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[889.38, 1169.08, 1901.7]</t>
+          <t>[2058.87, 1826.05, 1645.96]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[852.53, 1126.55, 2123.03]</t>
+          <t>[2212.19, 1876.09, 1610.32]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>131.8488906187104</v>
+        <v>95.36237235538681</v>
       </c>
       <c r="G5" t="n">
-        <v>100.2369197426425</v>
+        <v>79.6676461751794</v>
       </c>
       <c r="H5" t="n">
-        <v>6.174385126038068</v>
+        <v>3.937106579375688</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[1165.64, 1897.49, 1059.77]</t>
+          <t>[1837.93, 1657.53, 992.25]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1126.55, 2123.03, 1113.91]</t>
+          <t>[1876.09, 1610.32, 1067.0]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>135.8017294814568</v>
+        <v>55.5960886943792</v>
       </c>
       <c r="G6" t="n">
-        <v>106.2567388633433</v>
+        <v>53.37419841224217</v>
       </c>
       <c r="H6" t="n">
-        <v>6.317964287826565</v>
+        <v>3.990504531679167</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[1892.16, 1056.96, 919.2]</t>
+          <t>[1661.2, 995.89, 1072.12]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[2123.03, 1113.91, 995.56]</t>
+          <t>[1610.32, 1067.0, 1190.29]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>144.1923197355248</v>
+        <v>84.87027949812882</v>
       </c>
       <c r="G7" t="n">
-        <v>121.3926407026982</v>
+        <v>80.05210770038441</v>
       </c>
       <c r="H7" t="n">
-        <v>7.88572834977496</v>
+        <v>6.58392242755214</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[1066.07, 928.39, 1299.9]</t>
+          <t>[992.59, 1068.31, 884.98]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[1113.91, 995.56, 1304.96]</t>
+          <t>[1067.0, 1190.29, 936.82]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>47.70000075621635</v>
+        <v>87.75595149651893</v>
       </c>
       <c r="G8" t="n">
-        <v>40.02394131403654</v>
+        <v>82.743301604618</v>
       </c>
       <c r="H8" t="n">
-        <v>3.809864999136123</v>
+        <v>7.585095710661856</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[931.67, 1304.68, 981.26]</t>
+          <t>[1073.69, 892.13, 1183.45]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[995.56, 1304.96, 1013.53]</t>
+          <t>[1190.29, 936.82, 1068.99]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41.3262509800898</v>
+        <v>97.7986390045215</v>
       </c>
       <c r="G9" t="n">
-        <v>32.14749613921109</v>
+        <v>91.91652911285625</v>
       </c>
       <c r="H9" t="n">
-        <v>3.207696411767892</v>
+        <v>8.424535181403343</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1311.76, 986.56, 2054.63]</t>
+          <t>[904.51, 1198.36, 2117.33]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[1304.96, 1013.53, 2212.19]</t>
+          <t>[936.82, 1068.99, 2008.72]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>92.37526946507239</v>
+        <v>99.28944426982065</v>
       </c>
       <c r="G10" t="n">
-        <v>63.77982679921013</v>
+        <v>90.09394152994928</v>
       </c>
       <c r="H10" t="n">
-        <v>3.435056215363165</v>
+        <v>6.9857413208065</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[986.05, 2053.6, 1821.92]</t>
+          <t>[1205.1, 2128.69, 1140.04]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[1013.53, 2212.19, 1876.09]</t>
+          <t>[1068.99, 2008.72, 1050.06]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>98.04625449483787</v>
+        <v>116.9295141843408</v>
       </c>
       <c r="G11" t="n">
-        <v>80.07748855021289</v>
+        <v>115.3569410260641</v>
       </c>
       <c r="H11" t="n">
-        <v>4.255725856390604</v>
+        <v>9.091634367871874</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[1658.62, 844.24, 1794.56]</t>
+          <t>[996.19, 1576.97, 1854.81]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[1595.0, 775.1, 1554.73]</t>
+          <t>[973.73, 1772.95, 1911.34]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>148.7105476419636</v>
+        <v>118.4744111045723</v>
       </c>
       <c r="G12" t="n">
-        <v>124.1960620042239</v>
+        <v>91.65825710576617</v>
       </c>
       <c r="H12" t="n">
-        <v>9.444902807427964</v>
+        <v>5.439492928668132</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[835.47, 1776.26, 1484.6]</t>
+          <t>[1567.06, 1843.49, 2599.82]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[775.1, 1554.73, 1422.49]</t>
+          <t>[1772.95, 1911.34, 3120.12]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>137.3305146952765</v>
+        <v>325.4238036633956</v>
       </c>
       <c r="G13" t="n">
-        <v>114.6707362211711</v>
+        <v>264.67785367326</v>
       </c>
       <c r="H13" t="n">
-        <v>8.801314861740856</v>
+        <v>10.61270510323269</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[1741.26, 1455.78, 1276.01]</t>
+          <t>[1906.2, 2687.37, 5523.12]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[1554.73, 1422.49, 1438.45]</t>
+          <t>[1911.34, 3120.12, 4772.26]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>144.0934427298526</v>
+        <v>500.363673455829</v>
       </c>
       <c r="G14" t="n">
-        <v>127.421185050721</v>
+        <v>396.2513355215506</v>
       </c>
       <c r="H14" t="n">
-        <v>8.543599833660672</v>
+        <v>9.957532822991329</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[1412.1, 1238.02, 2256.27]</t>
+          <t>[2689.54, 5527.27, 1753.24]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[1422.49, 1438.45, 2569.91]</t>
+          <t>[3120.12, 4772.26, 1632.1]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>214.9842594316252</v>
+        <v>506.6622453999553</v>
       </c>
       <c r="G15" t="n">
-        <v>174.8244859553846</v>
+        <v>435.5785725259274</v>
       </c>
       <c r="H15" t="n">
-        <v>8.956428025139971</v>
+        <v>12.34782562741507</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[1240.7, 2260.94, 1019.89]</t>
+          <t>[5761.92, 1827.43, 925.1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[1438.45, 2569.91, 1203.41]</t>
+          <t>[4772.26, 1632.1, 834.45]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>236.8192568560073</v>
+        <v>584.7494997739094</v>
       </c>
       <c r="G16" t="n">
-        <v>230.08180905573</v>
+        <v>425.2139854728248</v>
       </c>
       <c r="H16" t="n">
-        <v>13.67343801137772</v>
+        <v>14.52313661834618</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[2350.64, 1060.04, 946.38]</t>
+          <t>[1734.13, 878.18, 1855.48]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[2569.91, 1203.41, 973.73]</t>
+          <t>[1632.1, 834.45, 1715.21]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>152.0751964044128</v>
+        <v>103.2783185875488</v>
       </c>
       <c r="G17" t="n">
-        <v>129.9941301394205</v>
+        <v>95.34403597372948</v>
       </c>
       <c r="H17" t="n">
-        <v>7.75134286600179</v>
+        <v>6.556650126969833</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[1085.06, 968.66, 1533.99]</t>
+          <t>[864.3, 1826.25, 1539.78]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[1203.41, 973.73, 1772.95]</t>
+          <t>[834.45, 1715.21, 1757.48]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>153.9845142247459</v>
+        <v>142.1431952914461</v>
       </c>
       <c r="G18" t="n">
-        <v>120.7914868862975</v>
+        <v>119.5303008277551</v>
       </c>
       <c r="H18" t="n">
-        <v>7.944272875541092</v>
+        <v>7.479440674090046</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[996.19, 1576.97, 1854.81]</t>
+          <t>[1809.34, 1525.74, 1356.05]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[973.73, 1772.95, 1911.34]</t>
+          <t>[1715.21, 1757.48, 1457.7]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>118.4744111045723</v>
+        <v>155.8810090952901</v>
       </c>
       <c r="G19" t="n">
-        <v>91.65825710576617</v>
+        <v>142.5054850074769</v>
       </c>
       <c r="H19" t="n">
-        <v>5.439492928668132</v>
+        <v>8.548980787077243</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[1567.06, 1843.49, 2599.82]</t>
+          <t>[1504.29, 1337.16, 2430.71]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[1772.95, 1911.34, 3120.12]</t>
+          <t>[1757.48, 1457.7, 2493.35]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>325.4238036633956</v>
+        <v>165.8872324396808</v>
       </c>
       <c r="G20" t="n">
-        <v>264.67785367326</v>
+        <v>145.4530333351029</v>
       </c>
       <c r="H20" t="n">
-        <v>10.61270510323269</v>
+        <v>8.39576641352714</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[1906.2, 2687.37, 5523.12]</t>
+          <t>[1392.39, 2530.76, 1144.78]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[1911.34, 3120.12, 4772.26]</t>
+          <t>[1457.7, 2493.35, 1468.96]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>500.363673455829</v>
+        <v>192.1455146591123</v>
       </c>
       <c r="G21" t="n">
-        <v>396.2513355215506</v>
+        <v>142.3010762699002</v>
       </c>
       <c r="H21" t="n">
-        <v>9.957532822991329</v>
+        <v>9.349909282797281</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[628.97, 622.59, 3359.62]</t>
+          <t>[1592.73, 2383.75, 1533.52]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[407.0, 752.27, 2940.25]</t>
+          <t>[1573.54, 2522.07, 1535.1]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>283.9945513645135</v>
+        <v>80.62760691270682</v>
       </c>
       <c r="G22" t="n">
-        <v>257.0065484210988</v>
+        <v>53.02801200924159</v>
       </c>
       <c r="H22" t="n">
-        <v>28.68007815866888</v>
+        <v>2.268841471128319</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[539.38, 2963.68, 910.48]</t>
+          <t>[2375.27, 1528.06, 2563.37]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[752.27, 2940.25, 983.9]</t>
+          <t>[2522.07, 1535.1, 2563.15]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>130.7159692462214</v>
+        <v>84.85079809230483</v>
       </c>
       <c r="G23" t="n">
-        <v>103.2458922043462</v>
+        <v>51.35307878485688</v>
       </c>
       <c r="H23" t="n">
-        <v>12.18608278180801</v>
+        <v>2.0959125822655</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[3260.01, 997.22, 721.63]</t>
+          <t>[1555.16, 2608.95, 4516.45]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[2940.25, 983.9, 746.07]</t>
+          <t>[1535.1, 2563.15, 5168.28]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>185.3129919699023</v>
+        <v>377.4406752501206</v>
       </c>
       <c r="G24" t="n">
-        <v>119.1768491387428</v>
+        <v>239.2326596338775</v>
       </c>
       <c r="H24" t="n">
-        <v>5.168657083375155</v>
+        <v>5.235366393058968</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[965.73, 698.89, 1763.03]</t>
+          <t>[2599.03, 4499.23, 475.09]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[983.9, 746.07, 2097.7]</t>
+          <t>[2563.15, 5168.28, 549.47]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>195.4119941823961</v>
+        <v>389.2094759618363</v>
       </c>
       <c r="G25" t="n">
-        <v>133.3380960584647</v>
+        <v>259.7706688910894</v>
       </c>
       <c r="H25" t="n">
-        <v>8.041450966542223</v>
+        <v>9.294102097623741</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[703.38, 1774.39, 323.87]</t>
+          <t>[4480.99, 473.09, 794.04]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[746.07, 2097.7, 364.17]</t>
+          <t>[5168.28, 549.47, 727.18]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>189.7176431378938</v>
+        <v>401.1121107291016</v>
       </c>
       <c r="G26" t="n">
-        <v>135.4353821751415</v>
+        <v>276.8430189852028</v>
       </c>
       <c r="H26" t="n">
-        <v>10.73369130523049</v>
+        <v>12.13100985855344</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[1807.43, 329.72, 1501.68]</t>
+          <t>[493.88, 828.46, 3337.33]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[2097.7, 364.17, 1573.54]</t>
+          <t>[549.47, 727.18, 3248.83]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>173.7897602218353</v>
+        <v>84.0241505668686</v>
       </c>
       <c r="G27" t="n">
-        <v>132.1953837384271</v>
+        <v>81.7897931655959</v>
       </c>
       <c r="H27" t="n">
-        <v>9.288496184314649</v>
+        <v>8.923015621095063</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[344.31, 1567.01, 2345.22]</t>
+          <t>[857.39, 3455.36, 1149.57]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[364.17, 1573.54, 2522.07]</t>
+          <t>[727.18, 3248.83, 978.78]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>102.8137290794923</v>
+        <v>172.0280147165558</v>
       </c>
       <c r="G28" t="n">
-        <v>67.7456110136752</v>
+        <v>169.1786291083594</v>
       </c>
       <c r="H28" t="n">
-        <v>4.293477114893356</v>
+        <v>13.90425586384787</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[1592.73, 2383.75, 1533.52]</t>
+          <t>[3285.63, 1094.86, 816.42]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[1573.54, 2522.07, 1535.1]</t>
+          <t>[3248.83, 978.78, 787.7]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>80.62760691270682</v>
+        <v>72.23306066988064</v>
       </c>
       <c r="G29" t="n">
-        <v>53.02801200924159</v>
+        <v>60.53090244214896</v>
       </c>
       <c r="H29" t="n">
-        <v>2.268841471128319</v>
+        <v>5.545972523451765</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[2375.27, 1528.06, 2563.37]</t>
+          <t>[1091.28, 813.78, 2190.3]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[2522.07, 1535.1, 2563.15]</t>
+          <t>[978.78, 787.7, 2309.5]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84.85079809230483</v>
+        <v>95.81918592004297</v>
       </c>
       <c r="G30" t="n">
-        <v>51.35307878485688</v>
+        <v>85.92549789158117</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0959125822655</v>
+        <v>6.655278231999449</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[1555.16, 2608.95, 4516.45]</t>
+          <t>[787.82, 2119.8, 362.06]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[1535.1, 2563.15, 5168.28]</t>
+          <t>[787.7, 2309.5, 910.76]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>377.4406752501206</v>
+        <v>335.1911929263498</v>
       </c>
       <c r="G31" t="n">
-        <v>239.2326596338775</v>
+        <v>246.1716064866803</v>
       </c>
       <c r="H31" t="n">
-        <v>5.235366393058968</v>
+        <v>22.82506148764553</v>
       </c>
     </row>
     <row r="32">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[717.42, 841.52, 820.79]</t>
+          <t>[640.98, 1168.62, 1014.26]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[484.2, 801.9, 887.7]</t>
+          <t>[683.3, 1181.92, 1065.8]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>141.9359082971179</v>
+        <v>39.26106179699838</v>
       </c>
       <c r="G32" t="n">
-        <v>113.2492714303815</v>
+        <v>35.72047552095546</v>
       </c>
       <c r="H32" t="n">
-        <v>20.21459462227083</v>
+        <v>4.051542392871736</v>
       </c>
     </row>
     <row r="33">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[785.82, 762.05, 572.64]</t>
+          <t>[1180.13, 1024.64, 1229.57]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[801.9, 887.7, 549.4]</t>
+          <t>[1181.92, 1065.8, 1411.84]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>74.35390953598815</v>
+        <v>107.8893423773105</v>
       </c>
       <c r="G33" t="n">
-        <v>54.98802865958066</v>
+        <v>75.07351309076073</v>
       </c>
       <c r="H33" t="n">
-        <v>6.796350039345185</v>
+        <v>5.641159564323792</v>
       </c>
     </row>
     <row r="34">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[764.36, 574.38, 923.66]</t>
+          <t>[1024.87, 1229.85, 2456.66]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[887.7, 549.4, 924.2]</t>
+          <t>[1065.8, 1411.84, 2715.72]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>72.65780864576547</v>
+        <v>184.3103684393888</v>
       </c>
       <c r="G34" t="n">
-        <v>49.62049739242173</v>
+        <v>160.6628501881882</v>
       </c>
       <c r="H34" t="n">
-        <v>6.166487640362362</v>
+        <v>8.756792183185141</v>
       </c>
     </row>
     <row r="35">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[587.16, 944.22, 884.62]</t>
+          <t>[1237.06, 2470.3, 499.97]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[549.4, 924.2, 879.71]</t>
+          <t>[1411.84, 2715.72, 555.2]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>24.83868898296132</v>
+        <v>176.849850421704</v>
       </c>
       <c r="G35" t="n">
-        <v>20.89777178163051</v>
+        <v>158.4741348951935</v>
       </c>
       <c r="H35" t="n">
-        <v>3.199267950872638</v>
+        <v>10.45446650048552</v>
       </c>
     </row>
     <row r="36">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[935.02, 876.31, 469.31]</t>
+          <t>[2514.04, 507.64, 838.75]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[924.2, 879.71, 486.18]</t>
+          <t>[2715.72, 555.2, 934.8]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11.73526118518054</v>
+        <v>131.8617123534492</v>
       </c>
       <c r="G36" t="n">
-        <v>10.36239007634648</v>
+        <v>115.0964652270127</v>
       </c>
       <c r="H36" t="n">
-        <v>1.675488325312955</v>
+        <v>8.755825876167272</v>
       </c>
     </row>
     <row r="37">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[874.8, 468.5, 636.83]</t>
+          <t>[513.3, 848.05, 920.25]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[879.71, 486.18, 683.3]</t>
+          <t>[555.2, 934.8, 877.25]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28.84347249865076</v>
+        <v>60.9129629232351</v>
       </c>
       <c r="G37" t="n">
-        <v>23.01829816417465</v>
+        <v>57.21900664069884</v>
       </c>
       <c r="H37" t="n">
-        <v>3.664987864932671</v>
+        <v>7.243144094187476</v>
       </c>
     </row>
     <row r="38">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[468.91, 637.44, 1162.14]</t>
+          <t>[861.55, 933.53, 583.26]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[486.18, 683.3, 1181.92]</t>
+          <t>[934.8, 877.25, 667.5]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>30.50993251739273</v>
+        <v>72.17740167145638</v>
       </c>
       <c r="G38" t="n">
-        <v>27.63549892692881</v>
+        <v>71.25518018960706</v>
       </c>
       <c r="H38" t="n">
-        <v>3.978827785595975</v>
+        <v>8.956983697032953</v>
       </c>
     </row>
     <row r="39">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[640.98, 1168.62, 1014.26]</t>
+          <t>[948.56, 593.21, 999.64]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[683.3, 1181.92, 1065.8]</t>
+          <t>[877.25, 667.5, 1008.2]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>39.26106179699838</v>
+        <v>59.65916755705737</v>
       </c>
       <c r="G39" t="n">
-        <v>35.72047552095546</v>
+        <v>51.38646290225969</v>
       </c>
       <c r="H39" t="n">
-        <v>4.051542392871736</v>
+        <v>6.702445260563724</v>
       </c>
     </row>
     <row r="40">
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[1180.13, 1024.64, 1229.57]</t>
+          <t>[584.61, 985.07, 936.85]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[1181.92, 1065.8, 1411.84]</t>
+          <t>[667.5, 1008.2, 720.25]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>107.8893423773105</v>
+        <v>134.5640880518557</v>
       </c>
       <c r="G40" t="n">
-        <v>75.07351309076073</v>
+        <v>107.5389318868226</v>
       </c>
       <c r="H40" t="n">
-        <v>5.641159564323792</v>
+        <v>14.92824705236082</v>
       </c>
     </row>
     <row r="41">
@@ -1882,32 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[1024.87, 1229.85, 2456.66]</t>
+          <t>[1009.1, 959.2, 526.86]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[1065.8, 1411.84, 2715.72]</t>
+          <t>[1008.2, 720.25, 492.3]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>184.3103684393888</v>
+        <v>139.3962183111095</v>
       </c>
       <c r="G41" t="n">
-        <v>160.6628501881882</v>
+        <v>91.47055103622841</v>
       </c>
       <c r="H41" t="n">
-        <v>8.756792183185141</v>
+        <v>13.4284232399993</v>
       </c>
     </row>
     <row r="42">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[661.41, 799.97, 991.46]</t>
+          <t>[2104.61, 3075.85, 1976.66]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[702.95, 819.01, 545.55]</t>
+          <t>[1694.58, 2388.17, 1805.18]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>258.7960086820798</v>
+        <v>472.7343039616953</v>
       </c>
       <c r="G42" t="n">
-        <v>168.8302743510696</v>
+        <v>423.0640019121752</v>
       </c>
       <c r="H42" t="n">
-        <v>29.9900715794735</v>
+        <v>20.83042719033698</v>
       </c>
     </row>
     <row r="43">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[828.92, 1026.88, 1149.29]</t>
+          <t>[2686.96, 1732.57, 2063.79]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[819.01, 545.55, 987.47]</t>
+          <t>[2388.17, 1805.18, 2375.43]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>293.2338288787489</v>
+        <v>252.7647319277291</v>
       </c>
       <c r="G43" t="n">
-        <v>217.6843367558506</v>
+        <v>227.6806992224249</v>
       </c>
       <c r="H43" t="n">
-        <v>35.27484458208779</v>
+        <v>9.884305410472834</v>
       </c>
     </row>
     <row r="44">
@@ -1990,32 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[1019.77, 1141.39, 1424.28]</t>
+          <t>[1602.12, 1905.8, 2219.77]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[545.55, 987.47, 1167.97]</t>
+          <t>[1805.18, 2375.43, 3235.58]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>323.6591772629166</v>
+        <v>656.671152746599</v>
       </c>
       <c r="G44" t="n">
-        <v>294.8146340205164</v>
+        <v>562.8316836034127</v>
       </c>
       <c r="H44" t="n">
-        <v>41.48550020405526</v>
+        <v>20.80459971168027</v>
       </c>
     </row>
     <row r="45">
@@ -2026,32 +2026,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[902.04, 1084.98, 1480.69]</t>
+          <t>[2060.91, 2392.78, 666.0]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[987.47, 1167.97, 2232.18]</t>
+          <t>[2375.43, 3235.58, 694.36]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>439.2859080019169</v>
+        <v>519.6265429961447</v>
       </c>
       <c r="G45" t="n">
-        <v>306.6338747171057</v>
+        <v>395.2238433475239</v>
       </c>
       <c r="H45" t="n">
-        <v>16.47415469018101</v>
+        <v>14.45732657986074</v>
       </c>
     </row>
     <row r="46">
@@ -2062,32 +2062,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[1155.34, 1569.7, 1077.69]</t>
+          <t>[2609.67, 728.27, 854.27]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[1167.97, 2232.18, 1568.38]</t>
+          <t>[3235.58, 694.36, 910.63]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>476.0333025145104</v>
+        <v>363.3575201224541</v>
       </c>
       <c r="G46" t="n">
-        <v>388.6012368677546</v>
+        <v>238.7251537034084</v>
       </c>
       <c r="H46" t="n">
-        <v>20.68216703878552</v>
+        <v>10.13901338482301</v>
       </c>
     </row>
     <row r="47">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[1580.86, 1085.39, 1515.22]</t>
+          <t>[833.42, 979.27, 910.13]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[2232.18, 1568.38, 1694.58]</t>
+          <t>[694.36, 910.63, 592.57]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>479.4652698128541</v>
+        <v>204.0350171060057</v>
       </c>
       <c r="G47" t="n">
-        <v>437.888858384752</v>
+        <v>175.0861157522087</v>
       </c>
       <c r="H47" t="n">
-        <v>23.51942237218397</v>
+        <v>27.05150083054776</v>
       </c>
     </row>
     <row r="48">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[1347.15, 1907.04, 2767.79]</t>
+          <t>[873.26, 818.29, 1304.64]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[1568.38, 1694.58, 2388.17]</t>
+          <t>[910.63, 592.57, 1041.58]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>281.773464580401</v>
+        <v>201.284805724831</v>
       </c>
       <c r="G48" t="n">
-        <v>271.100778479726</v>
+        <v>175.3835716325277</v>
       </c>
       <c r="H48" t="n">
-        <v>14.17956609620018</v>
+        <v>22.48390416245478</v>
       </c>
     </row>
     <row r="49">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[2104.61, 3075.85, 1976.66]</t>
+          <t>[839.79, 1338.64, 1593.27]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[1694.58, 2388.17, 1805.18]</t>
+          <t>[592.57, 1041.58, 1239.36]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>472.7343039616953</v>
+        <v>302.5501833849909</v>
       </c>
       <c r="G49" t="n">
-        <v>423.0640019121752</v>
+        <v>299.3938691893993</v>
       </c>
       <c r="H49" t="n">
-        <v>20.83042719033698</v>
+        <v>32.93164616424929</v>
       </c>
     </row>
     <row r="50">
@@ -2206,32 +2206,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[2686.96, 1732.57, 2063.79]</t>
+          <t>[1126.11, 1339.67, 2017.28]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[2388.17, 1805.18, 2375.43]</t>
+          <t>[1041.58, 1239.36, 2347.63]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>252.7647319277291</v>
+        <v>205.2129574744706</v>
       </c>
       <c r="G50" t="n">
-        <v>227.6806992224249</v>
+        <v>171.7304532421792</v>
       </c>
       <c r="H50" t="n">
-        <v>9.884305410472834</v>
+        <v>10.0937312488523</v>
       </c>
     </row>
     <row r="51">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[1602.12, 1905.8, 2219.77]</t>
+          <t>[1274.07, 1915.3, 1245.32]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[1805.18, 2375.43, 3235.58]</t>
+          <t>[1239.36, 2347.63, 1570.65]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>656.671152746599</v>
+        <v>313.0273583818377</v>
       </c>
       <c r="G51" t="n">
-        <v>562.8316836034127</v>
+        <v>264.1251248486524</v>
       </c>
       <c r="H51" t="n">
-        <v>20.80459971168027</v>
+        <v>13.97652692930661</v>
       </c>
     </row>
     <row r="52">
@@ -2278,29 +2278,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0.6, 0.39, 0.4]</t>
+          <t>[-0.03, -0.16, -0.24]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.4542739585084322</v>
+        <v>0.1648618110250527</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4372517320301421</v>
+        <v>0.1420267852505195</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2316,29 +2316,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0.35, 0.36, 0.36]</t>
+          <t>[-0.16, -0.23, -0.04]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0.7, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.3573652662529453</v>
+        <v>0.1640913839412836</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3573434348822567</v>
+        <v>0.1426963852396201</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2354,29 +2354,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0.38, 0.39, 0.71]</t>
+          <t>[-0.23, -0.03, 0.94]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.312074578905079</v>
+        <v>0.3374622240734981</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2571687166880026</v>
+        <v>0.2641803343726236</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2392,29 +2392,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[0.36, 0.67, -0.19]</t>
+          <t>[-0.01, 0.97, 0.63]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.5]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.9985074822010171</v>
+        <v>0.4877492261936807</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6924489600003163</v>
+        <v>0.4022570565559256</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2430,29 +2430,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[0.63, -0.21, -0.32]</t>
+          <t>[0.97, 0.63, 0.51]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[0.7, 1.5, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.004625305651492</v>
+        <v>0.5712548662454595</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6977638964564066</v>
+        <v>0.5692657981206531</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2468,29 +2468,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[-0.21, -0.32, -0.12]</t>
+          <t>[1.12, 0.96, 0.86]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[1.5, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.004730021785678</v>
+        <v>0.8929633787138932</v>
       </c>
       <c r="G57" t="n">
-        <v>0.713676674046111</v>
+        <v>0.8471041339068982</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2506,29 +2506,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[-0.26, -0.05, -0.17]</t>
+          <t>[0.96, 0.86, 0.86]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.1838216293986121</v>
+        <v>0.7884511619591352</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1616397140244412</v>
+        <v>0.7582669505903242</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2544,29 +2544,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[-0.03, -0.16, -0.24]</t>
+          <t>[0.35, 0.35, 0.72]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.1648618110250527</v>
+        <v>0.4638482734313045</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1420267852505195</v>
+        <v>0.3754075279467928</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2582,29 +2582,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[-0.16, -0.23, -0.04]</t>
+          <t>[0.36, 0.72, -0.07]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.5]</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.1640913839412836</v>
+        <v>1.018315487900701</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1426963852396201</v>
+        <v>0.8826638309155013</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[-0.23, -0.03, 0.94]</t>
+          <t>[0.69, -0.09, -0.27]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 1.5, 2.2]</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.3374622240734981</v>
+        <v>1.741079266568731</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2641803343726236</v>
+        <v>1.58264163965599</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[2.52, 1.75, 3.37]</t>
+          <t>[2.28, 1.88, 2.62]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[3.9, 1.4, 4.4]</t>
+          <t>[1.8, 1.8, 2.0]</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.014778142576275</v>
+        <v>0.4555727985400134</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9205770266589649</v>
+        <v>0.3947302975194713</v>
       </c>
       <c r="H62" t="n">
-        <v>27.95009887362264</v>
+        <v>20.7847912613568</v>
       </c>
     </row>
     <row r="63">
@@ -2694,32 +2694,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[1.86, 3.54, 3.2]</t>
+          <t>[1.76, 2.47, 3.54]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[1.4, 4.4, 1.8]</t>
+          <t>[1.8, 2.0, 3.0]</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.9833519785656178</v>
+        <v>0.4138863438402643</v>
       </c>
       <c r="G63" t="n">
-        <v>0.905648583659047</v>
+        <v>0.3487988305507269</v>
       </c>
       <c r="H63" t="n">
-        <v>43.32591360539915</v>
+        <v>14.50815275163349</v>
       </c>
     </row>
     <row r="64">
@@ -2730,32 +2730,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[3.46, 3.12, 2.52]</t>
+          <t>[2.48, 3.56, 8.3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[4.4, 1.8, 1.8]</t>
+          <t>[2.0, 3.0, 6.1]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.024808164358784</v>
+        <v>1.338740947439771</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9942383484873986</v>
+        <v>1.078749117051738</v>
       </c>
       <c r="H64" t="n">
-        <v>44.92186881078494</v>
+        <v>26.21873699480011</v>
       </c>
     </row>
     <row r="65">
@@ -2766,32 +2766,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[3.2, 2.59, 2.25]</t>
+          <t>[3.4, 7.99, 2.04]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 1.2]</t>
+          <t>[3.0, 6.1, 5.0]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.109074765996388</v>
+        <v>2.038554596626012</v>
       </c>
       <c r="G65" t="n">
-        <v>1.08010493442266</v>
+        <v>1.747999880799611</v>
       </c>
       <c r="H65" t="n">
-        <v>69.72206011802888</v>
+        <v>34.47080402987484</v>
       </c>
     </row>
     <row r="66">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[2.45, 2.12, 1.51]</t>
+          <t>[7.79, 1.97, 1.22]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[1.8, 1.2, 0.99]</t>
+          <t>[6.1, 5.0, 1.6]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.7166674034753565</v>
+        <v>2.01146966239693</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6965514628841021</v>
+        <v>1.69667194846119</v>
       </c>
       <c r="H66" t="n">
-        <v>55.10994685935904</v>
+        <v>37.2726335114524</v>
       </c>
     </row>
     <row r="67">
@@ -2838,32 +2838,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[2.05, 1.45, 2.59]</t>
+          <t>[1.83, 1.11, 2.48]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[1.2, 0.99, 1.8]</t>
+          <t>[5.0, 1.6, 3.6]</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.7189505527975478</v>
+        <v>1.96386504790339</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6984675021069157</v>
+        <v>1.594906263167712</v>
       </c>
       <c r="H67" t="n">
-        <v>53.63989635030338</v>
+        <v>41.73678715484382</v>
       </c>
     </row>
     <row r="68">
@@ -2874,32 +2874,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[1.33, 2.41, 1.99]</t>
+          <t>[1.46, 3.04, 2.53]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0.99, 1.8, 1.8]</t>
+          <t>[1.6, 3.6, 2.3]</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.4162493338563467</v>
+        <v>0.3571856988451069</v>
       </c>
       <c r="G68" t="n">
-        <v>0.378743221852835</v>
+        <v>0.3100721105600665</v>
       </c>
       <c r="H68" t="n">
-        <v>26.15485434836908</v>
+        <v>11.47557528965191</v>
       </c>
     </row>
     <row r="69">
@@ -2910,32 +2910,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[2.28, 1.88, 2.62]</t>
+          <t>[3.08, 2.56, 2.09]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[1.8, 1.8, 2.0]</t>
+          <t>[3.6, 2.3, 1.8]</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.4555727985400134</v>
+        <v>0.3774303997700043</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3947302975194713</v>
+        <v>0.35844842401047</v>
       </c>
       <c r="H69" t="n">
-        <v>20.7847912613568</v>
+        <v>14.01127398111419</v>
       </c>
     </row>
     <row r="70">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[1.76, 2.47, 3.54]</t>
+          <t>[2.62, 2.14, 1.81]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[1.8, 2.0, 3.0]</t>
+          <t>[2.3, 1.8, 1.8]</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.4138863438402643</v>
+        <v>0.2686862194265481</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3487988305507269</v>
+        <v>0.2214852003129522</v>
       </c>
       <c r="H70" t="n">
-        <v>14.50815275163349</v>
+        <v>11.02824458385869</v>
       </c>
     </row>
     <row r="71">
@@ -2982,32 +2982,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[2.48, 3.56, 8.3]</t>
+          <t>[2.1, 1.77, 1.26]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[2.0, 3.0, 6.1]</t>
+          <t>[1.8, 1.8, 0.6]</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.338740947439771</v>
+        <v>0.4177191795921529</v>
       </c>
       <c r="G71" t="n">
-        <v>1.078749117051738</v>
+        <v>0.3287619556427058</v>
       </c>
       <c r="H71" t="n">
-        <v>26.21873699480011</v>
+        <v>42.57384109969711</v>
       </c>
     </row>
     <row r="72">
@@ -3018,32 +3018,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[265.63, 189.73, 118.14]</t>
+          <t>[39.24, 32.61, 53.5]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[113.99, 96.8, 56.44]</t>
+          <t>[614.17, 34.8, 44.34]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>108.6839253826895</v>
+        <v>331.9799484795905</v>
       </c>
       <c r="G72" t="n">
-        <v>102.0877706607832</v>
+        <v>195.4259062369575</v>
       </c>
       <c r="H72" t="n">
-        <v>112.7803274693037</v>
+        <v>40.18583597580427</v>
       </c>
     </row>
     <row r="73">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[136.23, 85.16, 73.26]</t>
+          <t>[64.63, 104.54, 90.76]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[96.8, 56.44, 41.7]</t>
+          <t>[34.8, 44.34, 55.41]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>33.54369695273644</v>
+        <v>43.8328635684152</v>
       </c>
       <c r="G73" t="n">
-        <v>33.23657188106746</v>
+        <v>41.79523003265714</v>
       </c>
       <c r="H73" t="n">
-        <v>55.76690992348507</v>
+        <v>95.09846881997906</v>
       </c>
     </row>
     <row r="74">
@@ -3090,32 +3090,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[75.84, 65.34, 68.55]</t>
+          <t>[82.14, 71.59, 94.21]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[56.44, 41.7, 44.48]</t>
+          <t>[44.34, 55.41, 78.62]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>22.46787543216838</v>
+        <v>25.38490957490503</v>
       </c>
       <c r="G74" t="n">
-        <v>22.36878824141293</v>
+        <v>23.18644307389222</v>
       </c>
       <c r="H74" t="n">
-        <v>48.38996441096219</v>
+        <v>44.7535691791727</v>
       </c>
     </row>
     <row r="75">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[58.41, 61.38, 45.39]</t>
+          <t>[63.76, 84.11, 165.05]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[41.7, 44.48, 30.4]</t>
+          <t>[55.41, 78.62, 86.1]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>16.224328893696</v>
+        <v>45.9462558710872</v>
       </c>
       <c r="G75" t="n">
-        <v>16.2014658434549</v>
+        <v>30.9307741426948</v>
       </c>
       <c r="H75" t="n">
-        <v>42.46159081894223</v>
+        <v>37.91777678883327</v>
       </c>
     </row>
     <row r="76">
@@ -3162,32 +3162,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[53.14, 39.43, 56.32]</t>
+          <t>[82.36, 161.69, 119.71]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[44.48, 30.4, 63.4]</t>
+          <t>[78.62, 86.1, 60.7]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8.300088354159293</v>
+        <v>55.4095247045224</v>
       </c>
       <c r="G76" t="n">
-        <v>8.257036617148245</v>
+        <v>46.11494128237117</v>
       </c>
       <c r="H76" t="n">
-        <v>20.11447660799601</v>
+        <v>63.25794576091367</v>
       </c>
     </row>
     <row r="77">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[36.43, 52.1, 37.74]</t>
+          <t>[160.62, 118.93, 73.72]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[30.4, 63.4, 614.17]</t>
+          <t>[86.1, 60.7, 46.8]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>332.8850850947005</v>
+        <v>56.76863956190999</v>
       </c>
       <c r="G77" t="n">
-        <v>197.9197806133785</v>
+        <v>53.22235866089223</v>
       </c>
       <c r="H77" t="n">
-        <v>43.83660297650086</v>
+        <v>80.00019921599578</v>
       </c>
     </row>
     <row r="78">
@@ -3234,32 +3234,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[48.06, 34.82, 28.97]</t>
+          <t>[109.21, 67.76, 57.08]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[63.4, 614.17, 34.8]</t>
+          <t>[60.7, 46.8, 44.4]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>334.6214348726528</v>
+        <v>31.37363380420314</v>
       </c>
       <c r="G78" t="n">
-        <v>200.1737411471785</v>
+        <v>27.38032183741617</v>
       </c>
       <c r="H78" t="n">
-        <v>45.09484540974874</v>
+        <v>51.08120341010572</v>
       </c>
     </row>
     <row r="79">
@@ -3270,32 +3270,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[39.24, 32.61, 53.5]</t>
+          <t>[62.54, 52.73, 55.7]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[614.17, 34.8, 44.34]</t>
+          <t>[46.8, 44.4, 35.5]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>331.9799484795905</v>
+        <v>15.54835080891312</v>
       </c>
       <c r="G79" t="n">
-        <v>195.4259062369575</v>
+        <v>14.75719604377678</v>
       </c>
       <c r="H79" t="n">
-        <v>40.18583597580427</v>
+        <v>36.43297546134441</v>
       </c>
     </row>
     <row r="80">
@@ -3306,32 +3306,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[64.63, 104.54, 90.76]</t>
+          <t>[50.45, 53.33, 38.54]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[34.8, 44.34, 55.41]</t>
+          <t>[44.4, 35.5, 38.6]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>43.8328635684152</v>
+        <v>10.87080000456068</v>
       </c>
       <c r="G80" t="n">
-        <v>41.79523003265714</v>
+        <v>7.979491494473931</v>
       </c>
       <c r="H80" t="n">
-        <v>95.09846881997906</v>
+        <v>21.33407047017284</v>
       </c>
     </row>
     <row r="81">
@@ -3342,32 +3342,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[82.14, 71.59, 94.21]</t>
+          <t>[52.23, 37.77, 57.03]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[44.34, 55.41, 78.62]</t>
+          <t>[35.5, 38.6, 49.2]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>25.38490957490503</v>
+        <v>10.67290596597025</v>
       </c>
       <c r="G81" t="n">
-        <v>23.18644307389222</v>
+        <v>8.461724763010835</v>
       </c>
       <c r="H81" t="n">
-        <v>44.7535691791727</v>
+        <v>21.72632909669578</v>
       </c>
     </row>
     <row r="82">
@@ -3378,32 +3378,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[1449.86, 930.77, 1572.36]</t>
+          <t>[1700.05, 2197.16, 1378.64]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[1439.06, 901.1, 1509.3]</t>
+          <t>[1742.9, 2303.53, 1405.9]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>40.71435079548564</v>
+        <v>68.05491824801007</v>
       </c>
       <c r="G82" t="n">
-        <v>34.50753046978036</v>
+        <v>58.82786441826178</v>
       </c>
       <c r="H82" t="n">
-        <v>2.740226406363734</v>
+        <v>3.005126452556786</v>
       </c>
     </row>
     <row r="83">
@@ -3414,32 +3414,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[929.01, 1569.27, 947.74]</t>
+          <t>[2213.76, 1388.75, 1668.68]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[901.1, 1509.3, 912.27]</t>
+          <t>[2303.53, 1405.9, 1636.1]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>43.3337288750709</v>
+        <v>56.01805098351214</v>
       </c>
       <c r="G83" t="n">
-        <v>41.11575150870468</v>
+        <v>46.49989437451245</v>
       </c>
       <c r="H83" t="n">
-        <v>3.6528009094231</v>
+        <v>2.369422276872681</v>
       </c>
     </row>
     <row r="84">
@@ -3450,32 +3450,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[1555.54, 939.52, 1433.49]</t>
+          <t>[1405.35, 1689.04, 1092.4]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[1509.3, 912.27, 1510.78]</t>
+          <t>[1405.9, 1636.1, 1029.92]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>54.32759270079829</v>
+        <v>47.28076227100171</v>
       </c>
       <c r="G84" t="n">
-        <v>50.25989450242192</v>
+        <v>38.65689691020847</v>
       </c>
       <c r="H84" t="n">
-        <v>3.722232346814067</v>
+        <v>3.113756760460119</v>
       </c>
     </row>
     <row r="85">
@@ -3486,32 +3486,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[931.02, 1420.73, 1771.67]</t>
+          <t>[1689.24, 1092.53, 1498.07]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[912.27, 1510.78, 2160.7]</t>
+          <t>[1636.1, 1029.92, 1469.9]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>230.7981111347905</v>
+        <v>50.1260952007769</v>
       </c>
       <c r="G85" t="n">
-        <v>165.9414660624799</v>
+        <v>47.97507840317788</v>
       </c>
       <c r="H85" t="n">
-        <v>8.673365477106419</v>
+        <v>3.747989534116125</v>
       </c>
     </row>
     <row r="86">
@@ -3522,32 +3522,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[1440.92, 1853.45, 541.68]</t>
+          <t>[1082.9, 1483.99, 951.81]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[1510.78, 2160.7, 567.3]</t>
+          <t>[1029.92, 1469.9, 903.7]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>182.5193735300784</v>
+        <v>42.1137728591126</v>
       </c>
       <c r="G86" t="n">
-        <v>134.2453894775871</v>
+        <v>38.39582363736861</v>
       </c>
       <c r="H86" t="n">
-        <v>7.786930273120954</v>
+        <v>3.809029950838653</v>
       </c>
     </row>
     <row r="87">
@@ -3558,32 +3558,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[1892.77, 548.94, 1630.97]</t>
+          <t>[1462.31, 937.51, 1571.38]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[2160.7, 567.3, 1742.9]</t>
+          <t>[1469.9, 903.7, 1540.2]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>167.9796028543445</v>
+        <v>26.91504030580888</v>
       </c>
       <c r="G87" t="n">
-        <v>132.740762388113</v>
+        <v>24.19443706679552</v>
       </c>
       <c r="H87" t="n">
-        <v>7.35297962778186</v>
+        <v>2.09413840649104</v>
       </c>
     </row>
     <row r="88">
@@ -3594,32 +3594,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[564.85, 1697.98, 2194.54]</t>
+          <t>[938.93, 1573.75, 957.01]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[567.3, 1742.9, 2303.53]</t>
+          <t>[903.7, 1540.2, 962.22]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>68.07565319015615</v>
+        <v>28.24804286752036</v>
       </c>
       <c r="G88" t="n">
-        <v>52.12069915628092</v>
+        <v>24.66446952992972</v>
       </c>
       <c r="H88" t="n">
-        <v>2.580306354332934</v>
+        <v>2.206141702341788</v>
       </c>
     </row>
     <row r="89">
@@ -3630,32 +3630,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[1700.05, 2197.16, 1378.64]</t>
+          <t>[1556.26, 946.31, 1515.07]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[1742.9, 2303.53, 1405.9]</t>
+          <t>[1540.2, 962.22, 1525.3]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>68.05491824801007</v>
+        <v>14.32600616490231</v>
       </c>
       <c r="G89" t="n">
-        <v>58.82786441826178</v>
+        <v>14.06606067270472</v>
       </c>
       <c r="H89" t="n">
-        <v>3.005126452556786</v>
+        <v>1.122251180528515</v>
       </c>
     </row>
     <row r="90">
@@ -3666,32 +3666,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[2213.76, 1388.75, 1668.68]</t>
+          <t>[943.43, 1510.59, 2042.29]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[2303.53, 1405.9, 1636.1]</t>
+          <t>[962.22, 1525.3, 2182.3]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>56.01805098351214</v>
+        <v>82.00225453922323</v>
       </c>
       <c r="G90" t="n">
-        <v>46.49989437451245</v>
+        <v>57.83842522122757</v>
       </c>
       <c r="H90" t="n">
-        <v>2.369422276872681</v>
+        <v>3.111097584709465</v>
       </c>
     </row>
     <row r="91">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[1405.35, 1689.04, 1092.4]</t>
+          <t>[1519.07, 2053.08, 559.43]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[1405.9, 1636.1, 1029.92]</t>
+          <t>[1525.3, 2182.3, 646.8]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>47.28076227100171</v>
+        <v>90.12932262838812</v>
       </c>
       <c r="G91" t="n">
-        <v>38.65689691020847</v>
+        <v>74.27231547371684</v>
       </c>
       <c r="H91" t="n">
-        <v>3.113756760460119</v>
+        <v>6.612420712177625</v>
       </c>
     </row>
     <row r="92">
@@ -3738,32 +3738,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[737.57, 754.16, 937.29]</t>
+          <t>[577.55, 1359.68, 775.16]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[745.2, 883.08, 1073.09]</t>
+          <t>[609.67, 1386.95, 776.47]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>108.1972458407931</v>
+        <v>24.34061590821178</v>
       </c>
       <c r="G92" t="n">
-        <v>90.78447150769834</v>
+        <v>20.23424757403476</v>
       </c>
       <c r="H92" t="n">
-        <v>9.426092104449797</v>
+        <v>2.467941872327919</v>
       </c>
     </row>
     <row r="93">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[756.22, 939.98, 992.19]</t>
+          <t>[1379.39, 786.95, 1318.61]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[883.08, 1073.09, 982.9]</t>
+          <t>[1386.95, 776.47, 1380.59]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>106.2979408417096</v>
+        <v>36.55241601299995</v>
       </c>
       <c r="G93" t="n">
-        <v>89.75245107148355</v>
+        <v>26.67464374051675</v>
       </c>
       <c r="H93" t="n">
-        <v>9.238266254842337</v>
+        <v>2.128238254972152</v>
       </c>
     </row>
     <row r="94">
@@ -3810,32 +3810,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[986.39, 1042.15, 1033.55]</t>
+          <t>[788.14, 1320.61, 2591.8]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[1073.09, 982.9, 916.4]</t>
+          <t>[776.47, 1380.59, 3056.44]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>90.83462305101791</v>
+        <v>270.5670272224505</v>
       </c>
       <c r="G94" t="n">
-        <v>87.70241351147199</v>
+        <v>178.7612781149178</v>
       </c>
       <c r="H94" t="n">
-        <v>8.96400013310023</v>
+        <v>7.016406300809859</v>
       </c>
     </row>
     <row r="95">
@@ -3846,32 +3846,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[1072.04, 1060.92, 1914.26]</t>
+          <t>[1315.32, 2581.44, 737.71]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[982.9, 916.4, 1604.36]</t>
+          <t>[1380.59, 3056.44, 802.51]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>204.0189550083886</v>
+        <v>279.3334167662044</v>
       </c>
       <c r="G95" t="n">
-        <v>181.1877327054557</v>
+        <v>201.6887762417291</v>
       </c>
       <c r="H95" t="n">
-        <v>14.71863346503605</v>
+        <v>9.447646088868622</v>
       </c>
     </row>
     <row r="96">
@@ -3882,32 +3882,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[1035.04, 1867.32, 539.51]</t>
+          <t>[2613.17, 746.61, 854.04]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[916.4, 1604.36, 501.65]</t>
+          <t>[3056.44, 802.51, 900.05]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>167.986641549719</v>
+        <v>259.3121668345298</v>
       </c>
       <c r="G96" t="n">
-        <v>139.8227682810883</v>
+        <v>181.7261163038802</v>
       </c>
       <c r="H96" t="n">
-        <v>12.29499832379712</v>
+        <v>8.860121729742367</v>
       </c>
     </row>
     <row r="97">
@@ -3918,32 +3918,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[1811.06, 523.97, 596.56]</t>
+          <t>[773.78, 885.68, 1052.66]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[1604.36, 501.65, 609.67]</t>
+          <t>[802.51, 900.05, 1034.46]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>120.2732250705248</v>
+        <v>21.31599544385672</v>
       </c>
       <c r="G97" t="n">
-        <v>80.71210349501655</v>
+        <v>20.43309727370426</v>
       </c>
       <c r="H97" t="n">
-        <v>6.494624518962847</v>
+        <v>2.311939599440786</v>
       </c>
     </row>
     <row r="98">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[509.2, 579.83, 1365.29]</t>
+          <t>[892.85, 1061.2, 985.87]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[501.65, 609.67, 1386.95]</t>
+          <t>[900.05, 1034.46, 1049.59]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>21.7301240419376</v>
+        <v>40.11416959521772</v>
       </c>
       <c r="G98" t="n">
-        <v>19.68343380318396</v>
+        <v>32.55533420008074</v>
       </c>
       <c r="H98" t="n">
-        <v>2.653801768990685</v>
+        <v>3.152138527953785</v>
       </c>
     </row>
     <row r="99">
@@ -3990,32 +3990,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[577.55, 1359.68, 775.16]</t>
+          <t>[1063.1, 987.63, 944.61]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[609.67, 1386.95, 776.47]</t>
+          <t>[1034.46, 1049.59, 1000.72]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>24.34061590821178</v>
+        <v>51.01452327906437</v>
       </c>
       <c r="G99" t="n">
-        <v>20.23424757403476</v>
+        <v>48.90220211965804</v>
       </c>
       <c r="H99" t="n">
-        <v>2.467941872327919</v>
+        <v>4.759499448555995</v>
       </c>
     </row>
     <row r="100">
@@ -4026,32 +4026,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[1379.39, 786.95, 1318.61]</t>
+          <t>[981.55, 938.69, 1687.19]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[1386.95, 776.47, 1380.59]</t>
+          <t>[1049.59, 1000.72, 1661.76]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>36.55241601299995</v>
+        <v>55.1458330941793</v>
       </c>
       <c r="G100" t="n">
-        <v>26.67464374051675</v>
+        <v>51.83101611544138</v>
       </c>
       <c r="H100" t="n">
-        <v>2.128238254972152</v>
+        <v>4.736933458101775</v>
       </c>
     </row>
     <row r="101">
@@ -4062,32 +4062,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[788.14, 1320.61, 2591.8]</t>
+          <t>[955.17, 1718.35, 539.52]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[776.47, 1380.59, 3056.44]</t>
+          <t>[1000.72, 1661.76, 642.32]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>270.5670272224505</v>
+        <v>72.67731870836445</v>
       </c>
       <c r="G101" t="n">
-        <v>178.7612781149178</v>
+        <v>68.31581573554813</v>
       </c>
       <c r="H101" t="n">
-        <v>7.016406300809859</v>
+        <v>7.987472825457583</v>
       </c>
     </row>
     <row r="102">
@@ -4098,32 +4098,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[1574.69, 942.92, 1523.01]</t>
+          <t>[1255.23, 2932.06, 1183.85]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[1268.71, 717.47, 1195.59]</t>
+          <t>[1277.95, 2785.86, 1091.65]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>289.6301902741445</v>
+        <v>100.6496946423727</v>
       </c>
       <c r="G102" t="n">
-        <v>286.2838947074763</v>
+        <v>87.03975217448927</v>
       </c>
       <c r="H102" t="n">
-        <v>27.64199126435413</v>
+        <v>5.157220357876991</v>
       </c>
     </row>
     <row r="103">
@@ -4134,32 +4134,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[874.79, 1419.25, 989.9]</t>
+          <t>[2963.6, 1196.64, 1848.37]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[717.47, 1195.59, 1174.95]</t>
+          <t>[2785.86, 1091.65, 1696.98]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>190.6287319348699</v>
+        <v>147.7992212130209</v>
       </c>
       <c r="G103" t="n">
-        <v>188.6772501758341</v>
+        <v>144.7066503467288</v>
       </c>
       <c r="H103" t="n">
-        <v>18.79454955520019</v>
+        <v>8.306190358002356</v>
       </c>
     </row>
     <row r="104">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[1282.57, 891.62, 961.28]</t>
+          <t>[1160.64, 1797.56, 7545.6]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[1195.59, 1174.95, 1198.78]</t>
+          <t>[1091.65, 1696.98, 7053.88]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>219.2770456197503</v>
+        <v>292.4963764805921</v>
       </c>
       <c r="G104" t="n">
-        <v>202.6021751344655</v>
+        <v>220.4295713657895</v>
       </c>
       <c r="H104" t="n">
-        <v>17.06693727996075</v>
+        <v>6.405950269731322</v>
       </c>
     </row>
     <row r="105">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[860.33, 928.44, 2472.97]</t>
+          <t>[1751.57, 7361.46, 1539.68]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[1174.95, 1198.78, 3412.44]</t>
+          <t>[1696.98, 7053.88, 1336.21]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>592.9243662978079</v>
+        <v>215.2417276829516</v>
       </c>
       <c r="G105" t="n">
-        <v>508.145106166834</v>
+        <v>188.5484103514967</v>
       </c>
       <c r="H105" t="n">
-        <v>25.61989385996397</v>
+        <v>7.601686410224498</v>
       </c>
     </row>
     <row r="106">
@@ -4242,32 +4242,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[1061.25, 2824.71, 640.2]</t>
+          <t>[7264.23, 1521.07, 925.66]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[1198.78, 3412.44, 904.67]</t>
+          <t>[7053.88, 1336.21, 779.29]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>380.4747271583384</v>
+        <v>182.4320679541084</v>
       </c>
       <c r="G106" t="n">
-        <v>329.9081784104311</v>
+        <v>180.526386290272</v>
       </c>
       <c r="H106" t="n">
-        <v>19.30964475553062</v>
+        <v>11.8663249421115</v>
       </c>
     </row>
     <row r="107">
@@ -4278,32 +4278,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[2956.67, 670.09, 1037.2]</t>
+          <t>[1503.65, 914.87, 1569.55]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[3412.44, 904.67, 1277.95]</t>
+          <t>[1336.21, 779.29, 1358.98]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>326.9628947586476</v>
+        <v>173.9333777420014</v>
       </c>
       <c r="G107" t="n">
-        <v>310.3662351762727</v>
+        <v>171.1969223134417</v>
       </c>
       <c r="H107" t="n">
-        <v>19.37489380571437</v>
+        <v>15.14118892401532</v>
       </c>
     </row>
     <row r="108">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[707.27, 1094.95, 2540.52]</t>
+          <t>[871.67, 1499.86, 1305.97]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[904.67, 1277.95, 2785.86]</t>
+          <t>[779.29, 1358.98, 1678.28]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>210.2730366652546</v>
+        <v>235.9329062453691</v>
       </c>
       <c r="G108" t="n">
-        <v>208.5772510056644</v>
+        <v>201.8543755172042</v>
       </c>
       <c r="H108" t="n">
-        <v>14.98192753112057</v>
+        <v>14.8014518245702</v>
       </c>
     </row>
     <row r="109">
@@ -4350,32 +4350,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[1255.23, 2932.06, 1183.85]</t>
+          <t>[1432.44, 1246.29, 1209.71]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[1277.95, 2785.86, 1091.65]</t>
+          <t>[1358.98, 1678.28, 1322.31]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100.6496946423727</v>
+        <v>261.2062788595345</v>
       </c>
       <c r="G109" t="n">
-        <v>87.03975217448927</v>
+        <v>206.015402593129</v>
       </c>
       <c r="H109" t="n">
-        <v>5.157220357876991</v>
+        <v>13.22025043207844</v>
       </c>
     </row>
     <row r="110">
@@ -4386,32 +4386,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[2963.6, 1196.64, 1848.37]</t>
+          <t>[1210.08, 1173.37, 3153.42]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[2785.86, 1091.65, 1696.98]</t>
+          <t>[1678.28, 1322.31, 3725.33]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>147.7992212130209</v>
+        <v>435.3067043578225</v>
       </c>
       <c r="G110" t="n">
-        <v>144.7066503467288</v>
+        <v>396.3502717596833</v>
       </c>
       <c r="H110" t="n">
-        <v>8.306190358002356</v>
+        <v>18.17108683478261</v>
       </c>
     </row>
     <row r="111">
@@ -4422,32 +4422,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[1160.64, 1797.56, 7545.6]</t>
+          <t>[1387.16, 3777.32, 923.25]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[1091.65, 1696.98, 7053.88]</t>
+          <t>[1322.31, 3725.33, 873.84]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>292.4963764805921</v>
+        <v>55.8270548736111</v>
       </c>
       <c r="G111" t="n">
-        <v>220.4295713657895</v>
+        <v>55.41694911581514</v>
       </c>
       <c r="H111" t="n">
-        <v>6.405950269731322</v>
+        <v>3.984763861328084</v>
       </c>
     </row>
     <row r="112">
@@ -4458,32 +4458,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[408.59, 285.54, 384.91]</t>
+          <t>[459.32, 456.08, 309.11]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[394.91, 268.01, 540.77]</t>
+          <t>[371.41, 407.3, 269.39]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>90.8986305109394</v>
+        <v>62.40787792330348</v>
       </c>
       <c r="G112" t="n">
-        <v>62.35654446930175</v>
+        <v>58.80017345955569</v>
       </c>
       <c r="H112" t="n">
-        <v>12.94213398938733</v>
+        <v>16.79582685099336</v>
       </c>
     </row>
     <row r="113">
@@ -4494,32 +4494,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[283.31, 381.92, 274.45]</t>
+          <t>[431.58, 292.64, 322.12]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[268.01, 540.77, 223.04]</t>
+          <t>[407.3, 269.39, 276.03]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>96.7995044296717</v>
+        <v>32.93904121930517</v>
       </c>
       <c r="G113" t="n">
-        <v>75.18698305102006</v>
+        <v>31.20970324276154</v>
       </c>
       <c r="H113" t="n">
-        <v>19.37777949089092</v>
+        <v>10.43067703195045</v>
       </c>
     </row>
     <row r="114">
@@ -4530,32 +4530,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[377.05, 271.01, 1337.9]</t>
+          <t>[287.83, 316.88, 731.44]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[540.77, 223.04, 1274.39]</t>
+          <t>[269.39, 276.03, 723.39]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>105.1027087069245</v>
+        <v>26.29213583554615</v>
       </c>
       <c r="G114" t="n">
-        <v>91.73478728658897</v>
+        <v>22.44809196882354</v>
       </c>
       <c r="H114" t="n">
-        <v>18.92219536991782</v>
+        <v>7.586296263235116</v>
       </c>
     </row>
     <row r="115">
@@ -4566,32 +4566,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[292.46, 1442.49, 1404.14]</t>
+          <t>[311.1, 718.29, 344.63]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[223.04, 1274.39, 1208.04]</t>
+          <t>[276.03, 723.39, 391.11]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>154.4142807273236</v>
+        <v>33.74303478374364</v>
       </c>
       <c r="G115" t="n">
-        <v>144.5387017684301</v>
+        <v>28.88182099081769</v>
       </c>
       <c r="H115" t="n">
-        <v>20.18219550884631</v>
+        <v>8.430887090031586</v>
       </c>
     </row>
     <row r="116">
@@ -4602,32 +4602,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[1368.48, 1332.74, 298.64]</t>
+          <t>[694.72, 333.39, 232.63]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[1274.39, 1208.04, 224.55]</t>
+          <t>[723.39, 391.11, 263.5]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>99.82041089521947</v>
+        <v>41.25756380410397</v>
       </c>
       <c r="G116" t="n">
-        <v>97.62630064442737</v>
+        <v>39.08674197184239</v>
       </c>
       <c r="H116" t="n">
-        <v>16.89953889764285</v>
+        <v>10.14551739877245</v>
       </c>
     </row>
     <row r="117">
@@ -4638,32 +4638,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[1314.28, 294.53, 493.45]</t>
+          <t>[337.16, 235.28, 330.78]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[1208.04, 224.55, 371.41]</t>
+          <t>[391.11, 263.5, 366.41]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>101.781520219799</v>
+        <v>40.72678317627221</v>
       </c>
       <c r="G117" t="n">
-        <v>99.42031842904589</v>
+        <v>39.26548753489749</v>
       </c>
       <c r="H117" t="n">
-        <v>24.27220451663059</v>
+        <v>11.40907689151168</v>
       </c>
     </row>
     <row r="118">
@@ -4674,32 +4674,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[289.62, 485.22, 481.53]</t>
+          <t>[244.39, 343.4, 233.75]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[224.55, 371.41, 407.3]</t>
+          <t>[263.5, 366.41, 216.41]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>86.97868738353286</v>
+        <v>19.96266266344658</v>
       </c>
       <c r="G118" t="n">
-        <v>84.3675825565423</v>
+        <v>19.82167255027568</v>
       </c>
       <c r="H118" t="n">
-        <v>25.94768844966734</v>
+        <v>7.182250450940085</v>
       </c>
     </row>
     <row r="119">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[459.32, 456.08, 309.11]</t>
+          <t>[349.82, 238.01, 1193.75]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[371.41, 407.3, 269.39]</t>
+          <t>[366.41, 216.41, 1214.16]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>62.40787792330348</v>
+        <v>19.65145735308601</v>
       </c>
       <c r="G119" t="n">
-        <v>58.80017345955569</v>
+        <v>19.53472301069612</v>
       </c>
       <c r="H119" t="n">
-        <v>16.79582685099336</v>
+        <v>5.396842059664174</v>
       </c>
     </row>
     <row r="120">
@@ -4746,32 +4746,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[431.58, 292.64, 322.12]</t>
+          <t>[240.71, 1207.07, 1173.81]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[407.3, 269.39, 276.03]</t>
+          <t>[216.41, 1214.16, 1154.83]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>32.93904121930517</v>
+        <v>18.26826682806718</v>
       </c>
       <c r="G120" t="n">
-        <v>31.20970324276154</v>
+        <v>16.79231287981859</v>
       </c>
       <c r="H120" t="n">
-        <v>10.43067703195045</v>
+        <v>4.485615929695994</v>
       </c>
     </row>
     <row r="121">
@@ -4782,32 +4782,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[287.83, 316.88, 731.44]</t>
+          <t>[1176.7, 1144.28, 251.91]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[269.39, 276.03, 723.39]</t>
+          <t>[1214.16, 1154.83, 250.09]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>26.29213583554615</v>
+        <v>22.49379866627741</v>
       </c>
       <c r="G121" t="n">
-        <v>22.44809196882354</v>
+        <v>16.61052002011584</v>
       </c>
       <c r="H121" t="n">
-        <v>7.586296263235116</v>
+        <v>1.575490378375001</v>
       </c>
     </row>
     <row r="122">
@@ -4818,32 +4818,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[886.77, 747.75, 795.36]</t>
+          <t>[825.49, 1036.08, 1166.66]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[779.05, 790.61, 722.0]</t>
+          <t>[624.89, 803.3, 940.25]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>79.20979472403556</v>
+        <v>220.3697600482991</v>
       </c>
       <c r="G122" t="n">
-        <v>74.64687714536747</v>
+        <v>219.9301351018385</v>
       </c>
       <c r="H122" t="n">
-        <v>9.802987409851731</v>
+        <v>28.38653093978045</v>
       </c>
     </row>
     <row r="123">
@@ -4854,32 +4854,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[718.31, 764.2, 787.85]</t>
+          <t>[948.07, 1066.88, 987.31]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[790.61, 722.0, 727.52]</t>
+          <t>[803.3, 940.25, 861.61]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>59.57500321464799</v>
+        <v>132.6549195575439</v>
       </c>
       <c r="G123" t="n">
-        <v>58.27567770351883</v>
+        <v>132.3641520039797</v>
       </c>
       <c r="H123" t="n">
-        <v>7.760625614253759</v>
+        <v>15.35922292222427</v>
       </c>
     </row>
     <row r="124">
@@ -4890,32 +4890,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[787.12, 811.13, 714.78]</t>
+          <t>[1020.6, 944.64, 1424.14]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[722.0, 727.52, 683.02]</t>
+          <t>[940.25, 861.61, 1488.29]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>63.87099177370042</v>
+        <v>76.29994712215715</v>
       </c>
       <c r="G124" t="n">
-        <v>60.15954295088287</v>
+        <v>75.84302849844198</v>
       </c>
       <c r="H124" t="n">
-        <v>8.386733148772262</v>
+        <v>7.497421567424229</v>
       </c>
     </row>
     <row r="125">
@@ -4926,32 +4926,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[790.59, 696.74, 769.46]</t>
+          <t>[923.63, 1392.32, 762.4]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[727.52, 683.02, 1139.98]</t>
+          <t>[861.61, 1488.29, 821.5]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>217.1401432807351</v>
+        <v>74.27551493827576</v>
       </c>
       <c r="G125" t="n">
-        <v>149.1002704611103</v>
+        <v>72.36559619259022</v>
       </c>
       <c r="H125" t="n">
-        <v>14.39299895632996</v>
+        <v>6.947101990509723</v>
       </c>
     </row>
     <row r="126">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[679.66, 750.64, 848.11]</t>
+          <t>[1364.32, 747.54, 740.15]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[683.02, 1139.98, 1046.42]</t>
+          <t>[1488.29, 821.5, 819.07]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>252.2725278161106</v>
+        <v>94.98778637543367</v>
       </c>
       <c r="G126" t="n">
-        <v>197.0038708717008</v>
+        <v>92.28463359916752</v>
       </c>
       <c r="H126" t="n">
-        <v>17.86555910433252</v>
+        <v>8.989425339480546</v>
       </c>
     </row>
     <row r="127">
@@ -4998,32 +4998,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[751.75, 849.37, 706.86]</t>
+          <t>[765.66, 759.19, 709.73]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[1139.98, 1046.42, 624.89]</t>
+          <t>[821.5, 819.07, 758.66]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>255.7817223901123</v>
+        <v>55.07002174286996</v>
       </c>
       <c r="G127" t="n">
-        <v>222.418259543697</v>
+        <v>54.88383938597152</v>
       </c>
       <c r="H127" t="n">
-        <v>22.00154116740499</v>
+        <v>6.852576569658093</v>
       </c>
     </row>
     <row r="128">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[961.9, 800.53, 1004.16]</t>
+          <t>[773.54, 723.16, 745.54]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[1046.42, 624.89, 803.3]</t>
+          <t>[819.07, 758.66, 872.49]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>161.5932566835661</v>
+        <v>80.51992887117295</v>
       </c>
       <c r="G128" t="n">
-        <v>153.6736126750955</v>
+        <v>69.32666796718001</v>
       </c>
       <c r="H128" t="n">
-        <v>20.39622211960688</v>
+        <v>8.262760407934673</v>
       </c>
     </row>
     <row r="129">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[825.49, 1036.08, 1166.66]</t>
+          <t>[734.18, 756.82, 710.03]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[624.89, 803.3, 940.25]</t>
+          <t>[758.66, 872.49, 578.73]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>220.3697600482991</v>
+        <v>102.012840541443</v>
       </c>
       <c r="G129" t="n">
-        <v>219.9301351018385</v>
+        <v>90.48444585904311</v>
       </c>
       <c r="H129" t="n">
-        <v>28.38653093978045</v>
+        <v>13.05748058249314</v>
       </c>
     </row>
     <row r="130">
@@ -5106,32 +5106,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[948.07, 1066.88, 987.31]</t>
+          <t>[763.52, 716.3, 1070.51]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[803.3, 940.25, 861.61]</t>
+          <t>[872.49, 578.73, 1190.92]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>132.6549195575439</v>
+        <v>122.8819252815224</v>
       </c>
       <c r="G130" t="n">
-        <v>132.3641520039797</v>
+        <v>122.3184320632344</v>
       </c>
       <c r="H130" t="n">
-        <v>15.35922292222427</v>
+        <v>15.4573257460962</v>
       </c>
     </row>
     <row r="131">
@@ -5142,32 +5142,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[1020.6, 944.64, 1424.14]</t>
+          <t>[743.39, 1107.23, 990.6]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[940.25, 861.61, 1488.29]</t>
+          <t>[578.73, 1190.92, 1070.66]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>76.29994712215715</v>
+        <v>116.2294411335687</v>
       </c>
       <c r="G131" t="n">
-        <v>75.84302849844198</v>
+        <v>109.4711797111833</v>
       </c>
       <c r="H131" t="n">
-        <v>7.497421567424229</v>
+        <v>14.31921462304567</v>
       </c>
     </row>
     <row r="132">
@@ -5178,32 +5178,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[121.72, 131.52, 49.42]</t>
+          <t>[138.4, 401.74, 228.72]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[98.7, 135.6, 42.3]</t>
+          <t>[146.4, 574.9, 234.6]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>14.10871748133552</v>
+        <v>100.1360451895951</v>
       </c>
       <c r="G132" t="n">
-        <v>11.40407490355462</v>
+        <v>62.34766186229869</v>
       </c>
       <c r="H132" t="n">
-        <v>14.3843137862011</v>
+        <v>12.69806679607791</v>
       </c>
     </row>
     <row r="133">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[138.48, 42.06, 130.79]</t>
+          <t>[402.34, 229.06, 338.95]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[135.6, 42.3, 133.5]</t>
+          <t>[574.9, 234.6, 311.6]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2.286040328391511</v>
+        <v>100.9241472957431</v>
       </c>
       <c r="G133" t="n">
-        <v>1.942363230650382</v>
+        <v>68.48635567989744</v>
       </c>
       <c r="H133" t="n">
-        <v>1.573307835006644</v>
+        <v>13.71903446997188</v>
       </c>
     </row>
     <row r="134">
@@ -5250,32 +5250,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[42.03, 130.71, 88.28]</t>
+          <t>[231.41, 342.75, 591.37]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[42.3, 133.5, 89.1]</t>
+          <t>[234.6, 311.6, 603.6]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1.684042884026335</v>
+        <v>19.40663105637344</v>
       </c>
       <c r="G134" t="n">
-        <v>1.291768544114762</v>
+        <v>15.51978006198425</v>
       </c>
       <c r="H134" t="n">
-        <v>1.213720914948914</v>
+        <v>4.459844812385837</v>
       </c>
     </row>
     <row r="135">
@@ -5286,32 +5286,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[130.74, 88.29, 329.5]</t>
+          <t>[342.94, 591.65, 102.02]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[133.5, 89.1, 328.8]</t>
+          <t>[311.6, 603.6, 90.9]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1.709077647471523</v>
+        <v>20.4020323684104</v>
       </c>
       <c r="G135" t="n">
-        <v>1.422227807876055</v>
+        <v>18.13643645160163</v>
       </c>
       <c r="H135" t="n">
-        <v>1.062015846332433</v>
+        <v>8.090207730131452</v>
       </c>
     </row>
     <row r="136">
@@ -5322,32 +5322,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[88.35, 329.69, 167.78]</t>
+          <t>[589.67, 101.85, 137.55]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[89.1, 328.8, 171.0]</t>
+          <t>[603.6, 90.9, 123.95]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1.976726377950242</v>
+        <v>12.8946076556927</v>
       </c>
       <c r="G136" t="n">
-        <v>1.620465512162014</v>
+        <v>12.82554234522193</v>
       </c>
       <c r="H136" t="n">
-        <v>0.9990184781299156</v>
+        <v>8.441157708550932</v>
       </c>
     </row>
     <row r="137">
@@ -5358,32 +5358,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[329.77, 167.82, 138.34]</t>
+          <t>[101.91, 137.63, 42.7]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[328.8, 171.0, 146.4]</t>
+          <t>[90.9, 123.95, 205.05]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>5.032378861315538</v>
+        <v>94.28064684992779</v>
       </c>
       <c r="G137" t="n">
-        <v>4.068524014393972</v>
+        <v>62.34789122754194</v>
       </c>
       <c r="H137" t="n">
-        <v>2.552716973708062</v>
+        <v>34.10893128725409</v>
       </c>
     </row>
     <row r="138">
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[167.81, 138.33, 401.56]</t>
+          <t>[137.18, 42.57, 133.87]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[171.0, 146.4, 574.9]</t>
+          <t>[123.95, 205.05, 131.6]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>100.2033756102241</v>
+        <v>94.12937622344857</v>
       </c>
       <c r="G138" t="n">
-        <v>61.53419436817347</v>
+        <v>59.32895564719212</v>
       </c>
       <c r="H138" t="n">
-        <v>12.51010077851295</v>
+        <v>30.54736461660285</v>
       </c>
     </row>
     <row r="139">
@@ -5430,32 +5430,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[138.4, 401.74, 228.72]</t>
+          <t>[42.45, 133.53, 89.31]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[146.4, 574.9, 234.6]</t>
+          <t>[205.05, 131.6, 193.7]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>100.1360451895951</v>
+        <v>111.5612022538092</v>
       </c>
       <c r="G139" t="n">
-        <v>62.34766186229869</v>
+        <v>89.63660616628761</v>
       </c>
       <c r="H139" t="n">
-        <v>12.69806679607791</v>
+        <v>44.88373115689297</v>
       </c>
     </row>
     <row r="140">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[402.34, 229.06, 338.95]</t>
+          <t>[139.87, 93.56, 345.84]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[574.9, 234.6, 311.6]</t>
+          <t>[131.6, 193.7, 305.8]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>100.9241472957431</v>
+        <v>62.45168141082794</v>
       </c>
       <c r="G140" t="n">
-        <v>68.48635567989744</v>
+        <v>49.48480832118869</v>
       </c>
       <c r="H140" t="n">
-        <v>13.71903446997188</v>
+        <v>23.69241001609229</v>
       </c>
     </row>
     <row r="141">
@@ -5502,32 +5502,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[231.41, 342.75, 591.37]</t>
+          <t>[93.15, 344.37, 178.29]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[234.6, 311.6, 603.6]</t>
+          <t>[193.7, 305.8, 159.6]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>19.40663105637344</v>
+        <v>63.10426814801403</v>
       </c>
       <c r="G141" t="n">
-        <v>15.51978006198425</v>
+        <v>52.60030230114523</v>
       </c>
       <c r="H141" t="n">
-        <v>4.459844812385837</v>
+        <v>25.40961763336503</v>
       </c>
     </row>
     <row r="142">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[6043.11, 3173.4, 4811.32]</t>
+          <t>[5516.23, 6530.01, 3655.03]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[6953.75, 3691.63, 5536.26]</t>
+          <t>[5536.26, 6364.54, 3964.6]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>735.6110013403428</v>
+        <v>202.9900200396775</v>
       </c>
       <c r="G142" t="n">
-        <v>717.9379721779529</v>
+        <v>165.0243715734127</v>
       </c>
       <c r="H142" t="n">
-        <v>13.40937582398904</v>
+        <v>3.590021652689702</v>
       </c>
     </row>
     <row r="143">
@@ -5574,32 +5574,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[3538.75, 5337.42, 6325.55]</t>
+          <t>[6547.9, 3664.61, 4320.1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[3691.63, 5536.26, 6364.54]</t>
+          <t>[6364.54, 3964.6, 3055.77]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>146.5463802737744</v>
+        <v>757.6591444443892</v>
       </c>
       <c r="G143" t="n">
-        <v>130.2343164603603</v>
+        <v>582.5598189608075</v>
       </c>
       <c r="H143" t="n">
-        <v>2.781770451996582</v>
+        <v>17.27426387948841</v>
       </c>
     </row>
     <row r="144">
@@ -5610,32 +5610,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[5516.23, 6530.01, 3655.03]</t>
+          <t>[3585.4, 4229.59, 6599.6]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[5536.26, 6364.54, 3964.6]</t>
+          <t>[3964.6, 3055.77, 6699.51]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>202.9900200396775</v>
+        <v>714.5212643806598</v>
       </c>
       <c r="G144" t="n">
-        <v>165.0243715734127</v>
+        <v>550.9756887890313</v>
       </c>
       <c r="H144" t="n">
-        <v>3.590021652689702</v>
+        <v>16.48970167772521</v>
       </c>
     </row>
     <row r="145">
@@ -5646,32 +5646,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[6547.9, 3664.61, 4320.1]</t>
+          <t>[4562.35, 7100.34, 1338.96]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[6364.54, 3964.6, 3055.77]</t>
+          <t>[3055.77, 6699.51, 1165.51]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>757.6591444443892</v>
+        <v>905.6378633276321</v>
       </c>
       <c r="G145" t="n">
-        <v>582.5598189608075</v>
+        <v>693.6198921233189</v>
       </c>
       <c r="H145" t="n">
-        <v>17.27426387948841</v>
+        <v>23.38920644691691</v>
       </c>
     </row>
     <row r="146">
@@ -5682,1472 +5682,2012 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[3585.4, 4229.59, 6599.6]</t>
+          <t>[5533.87, 1051.65, 1664.77]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[3964.6, 3055.77, 6699.51]</t>
+          <t>[6699.51, 1165.51, 1732.91]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>714.5212643806598</v>
+        <v>677.3294782903969</v>
       </c>
       <c r="G146" t="n">
-        <v>550.9756887890313</v>
+        <v>449.2129771031139</v>
       </c>
       <c r="H146" t="n">
-        <v>16.48970167772521</v>
+        <v>10.36666330764352</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[2891.53, 211.78, 1509.65]</t>
+          <t>[1177.98, 1858.11, 2314.79]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[3084.55, 225.4, 1580.6]</t>
+          <t>[1165.51, 1732.91, 2347.51]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>118.9919547495565</v>
+        <v>75.05909898743823</v>
       </c>
       <c r="G147" t="n">
-        <v>92.5328403063907</v>
+        <v>56.79766550152764</v>
       </c>
       <c r="H147" t="n">
-        <v>5.596996817348511</v>
+        <v>3.229588311951851</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[217.12, 1546.1, 1857.38]</t>
+          <t>[1848.55, 2303.03, 2529.77]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[225.4, 1580.6, 1976.4]</t>
+          <t>[1732.91, 2347.51, 2583.73]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>71.70648605158584</v>
+        <v>78.02280120621282</v>
       </c>
       <c r="G148" t="n">
-        <v>53.93256563369633</v>
+        <v>71.35976091113646</v>
       </c>
       <c r="H148" t="n">
-        <v>3.95875199525001</v>
+        <v>3.55212127065059</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[1561.95, 1875.4, 1140.79]</t>
+          <t>[2231.67, 2454.23, 3084.05]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[1580.6, 1976.4, 1158.11]</t>
+          <t>[2347.51, 2583.73, 3180.08]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>60.13365008085773</v>
+        <v>114.6142460609287</v>
       </c>
       <c r="G149" t="n">
-        <v>45.65496107607873</v>
+        <v>113.7874137985197</v>
       </c>
       <c r="H149" t="n">
-        <v>2.595162132942919</v>
+        <v>4.322055593561013</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[1882.42, 1144.61, 1463.96]</t>
+          <t>[2515.35, 3158.05, 6510.86]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[1976.4, 1158.11, 1406.9]</t>
+          <t>[2583.73, 3180.08, 5805.7]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>63.95364456643001</v>
+        <v>409.2316166580584</v>
       </c>
       <c r="G150" t="n">
-        <v>54.84616911008599</v>
+        <v>265.1884696437069</v>
       </c>
       <c r="H150" t="n">
-        <v>3.325471946421362</v>
+        <v>5.161714131195457</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[1160.19, 1483.25, 2812.56]</t>
+          <t>[3198.31, 6591.61, 3465.58]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[1158.11, 1406.9, 2867.79]</t>
+          <t>[3180.08, 5805.7, 6077.3]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>54.41755780676781</v>
+        <v>1574.700685078447</v>
       </c>
       <c r="G151" t="n">
-        <v>44.5534768363331</v>
+        <v>1138.618528434338</v>
       </c>
       <c r="H151" t="n">
-        <v>2.510809092147172</v>
+        <v>19.02835370578009</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[1538.63, 601.52, 907.24]</t>
+          <t>[1561.95, 1875.4, 1140.79]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[1521.4, 728.6, 944.9]</t>
+          <t>[1580.6, 1976.4, 1158.11]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>77.16938001706362</v>
+        <v>60.13365008085773</v>
       </c>
       <c r="G152" t="n">
-        <v>60.65783369424727</v>
+        <v>45.65496107607873</v>
       </c>
       <c r="H152" t="n">
-        <v>7.52004128524715</v>
+        <v>2.595162132942919</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[598.29, 902.72, 1676.91]</t>
+          <t>[1882.42, 1144.61, 1463.96]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[728.6, 944.9, 1715.0]</t>
+          <t>[1976.4, 1158.11, 1406.9]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>82.0801900934714</v>
+        <v>63.95364456643001</v>
       </c>
       <c r="G153" t="n">
-        <v>70.19422032671548</v>
+        <v>54.84616911008599</v>
       </c>
       <c r="H153" t="n">
-        <v>8.190165550057568</v>
+        <v>3.325471946421362</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[980.21, 1814.63, 739.09]</t>
+          <t>[1160.19, 1483.25, 2812.56]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[944.9, 1715.0, 661.8]</t>
+          <t>[1158.11, 1406.9, 2867.79]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>75.6038728937443</v>
+        <v>54.41755780676781</v>
       </c>
       <c r="G154" t="n">
-        <v>70.74475658071378</v>
+        <v>44.5534768363331</v>
       </c>
       <c r="H154" t="n">
-        <v>7.075136901966811</v>
+        <v>2.510809092147172</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[1785.66, 727.76, 870.53]</t>
+          <t>[1482.43, 2811.14, 1283.37]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[1715.0, 661.8, 836.6]</t>
+          <t>[1406.9, 2867.79, 1237.31]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>59.14867114780203</v>
+        <v>60.65207821987105</v>
       </c>
       <c r="G155" t="n">
-        <v>56.85284551017757</v>
+        <v>59.41422478373321</v>
       </c>
       <c r="H155" t="n">
-        <v>6.047782918564756</v>
+        <v>3.688866161907328</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[716.35, 857.41, 3869.52]</t>
+          <t>[2772.49, 1266.43, 1018.02]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[661.8, 836.6, 3939.0]</t>
+          <t>[2867.79, 1237.31, 1032.43]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>52.39532556065994</v>
+        <v>58.13010537324629</v>
       </c>
       <c r="G156" t="n">
-        <v>48.27972478750064</v>
+        <v>46.27505411385979</v>
       </c>
       <c r="H156" t="n">
-        <v>4.164606497485894</v>
+        <v>2.357322354896612</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[2702.41, 1670.64, 1581.84]</t>
+          <t>[1277.35, 1026.37, 1390.9]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[1473.51, 1514.97, 1347.13]</t>
+          <t>[1237.31, 1032.43, 1470.26]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>727.8991722730775</v>
+        <v>51.44015042650295</v>
       </c>
       <c r="G157" t="n">
-        <v>539.7589348979624</v>
+        <v>41.82037306338945</v>
       </c>
       <c r="H157" t="n">
-        <v>37.03255837800859</v>
+        <v>3.073581467757945</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[1431.52, 1357.4, 1335.61]</t>
+          <t>[1018.38, 1380.35, 360.02]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[1514.97, 1347.13, 1780.28]</t>
+          <t>[1032.43, 1470.26, 386.71]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>261.2787126760184</v>
+        <v>54.75270825671042</v>
       </c>
       <c r="G158" t="n">
-        <v>179.4624134475537</v>
+        <v>43.55213833094543</v>
       </c>
       <c r="H158" t="n">
-        <v>10.41602898092666</v>
+        <v>4.79312112883428</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[1385.17, 1362.5, 1509.72]</t>
+          <t>[1385.15, 361.22, 323.84]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[1347.13, 1780.28, 1950.87]</t>
+          <t>[1470.26, 386.71, 372.01]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>351.4729130271062</v>
+        <v>58.34728356763257</v>
       </c>
       <c r="G159" t="n">
-        <v>298.9892325279125</v>
+        <v>52.92170997865372</v>
       </c>
       <c r="H159" t="n">
-        <v>16.30123902220867</v>
+        <v>8.442619527963886</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[1351.33, 1497.41, 2376.91]</t>
+          <t>[366.43, 328.33, 3081.25]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[1780.28, 1950.87, 4776.34]</t>
+          <t>[386.71, 372.01, 3180.35]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1431.41965153199</v>
+        <v>63.61187256714159</v>
       </c>
       <c r="G160" t="n">
-        <v>1093.947219869844</v>
+        <v>54.35250958495177</v>
       </c>
       <c r="H160" t="n">
-        <v>32.52479057318629</v>
+        <v>6.70067239911938</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[1592.92, 2631.32, 1601.98]</t>
+          <t>[333.22, 3125.81, 228.39]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[1950.87, 4776.34, 2508.52]</t>
+          <t>[372.01, 3180.35, 264.57]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1360.278125334136</v>
+        <v>43.92386556960138</v>
       </c>
       <c r="G161" t="n">
-        <v>1136.505474396434</v>
+        <v>43.16873654287011</v>
       </c>
       <c r="H161" t="n">
-        <v>33.13205657527668</v>
+        <v>8.605409257334539</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[2742.57, 1686.12, 2308.26]</t>
+          <t>[980.21, 1814.63, 739.09]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[4776.34, 2508.52, 2132.52]</t>
+          <t>[944.9, 1715.0, 661.8]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1270.622170638349</v>
+        <v>75.6038728937443</v>
       </c>
       <c r="G162" t="n">
-        <v>1010.635235494654</v>
+        <v>70.74475658071378</v>
       </c>
       <c r="H162" t="n">
-        <v>27.86837695752153</v>
+        <v>7.075136901966811</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[1828.08, 2476.61, 3892.79]</t>
+          <t>[1785.66, 727.76, 870.53]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[2508.52, 2132.52, 2747.67]</t>
+          <t>[1715.0, 661.8, 836.6]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>794.2915590560185</v>
+        <v>59.14867114780203</v>
       </c>
       <c r="G163" t="n">
-        <v>723.2176633201007</v>
+        <v>56.85284551017757</v>
       </c>
       <c r="H163" t="n">
-        <v>28.31223773080823</v>
+        <v>6.047782918564756</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[3250.35, 3623.54, 3594.81]</t>
+          <t>[716.35, 857.41, 3869.52]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[2132.52, 2747.67, 2928.02]</t>
+          <t>[661.8, 836.6, 3939.0]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>905.7777735790343</v>
+        <v>52.39532556065994</v>
       </c>
       <c r="G164" t="n">
-        <v>886.8295966249128</v>
+        <v>48.27972478750064</v>
       </c>
       <c r="H164" t="n">
-        <v>35.68926375702126</v>
+        <v>4.164606497485894</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[4231.3, 2951.63, 2388.38]</t>
+          <t>[831.69, 3757.73, 2206.61]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[2747.67, 2928.02, 2811.94]</t>
+          <t>[836.6, 3939.0, 2126.0]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>890.9029254427408</v>
+        <v>114.5711513972124</v>
       </c>
       <c r="G165" t="n">
-        <v>643.5992012242788</v>
+        <v>88.92813227550486</v>
       </c>
       <c r="H165" t="n">
-        <v>23.28837023262556</v>
+        <v>2.993369429960825</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[2767.6, 2444.51, 3609.17]</t>
+          <t>[3766.32, 2211.91, 429.2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[2928.02, 2811.94, 4615.15]</t>
+          <t>[3939.0, 2126.0, 413.5]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>625.2311399327153</v>
+        <v>111.7229172048213</v>
       </c>
       <c r="G166" t="n">
-        <v>511.2771081497804</v>
+        <v>91.43111383646858</v>
       </c>
       <c r="H166" t="n">
-        <v>13.44763587094351</v>
+        <v>4.074016735677966</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[941.62, 307.49, 414.63]</t>
+          <t>[2249.57, 436.45, 823.72]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[977.96, 287.25, 477.49]</t>
+          <t>[2126.0, 413.5, 795.3]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>43.51612889115717</v>
+        <v>74.39557467027626</v>
       </c>
       <c r="G167" t="n">
-        <v>39.81106803709086</v>
+        <v>58.31479108035671</v>
       </c>
       <c r="H167" t="n">
-        <v>7.974970139631536</v>
+        <v>4.97898646583894</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[309.0, 416.54, 407.04]</t>
+          <t>[427.27, 806.88, 373.41]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[287.25, 477.49, 472.46]</t>
+          <t>[413.5, 795.3, 373.6]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>53.12850020683774</v>
+        <v>10.38701722056282</v>
       </c>
       <c r="G168" t="n">
-        <v>49.3739197082348</v>
+        <v>8.512091576906434</v>
       </c>
       <c r="H168" t="n">
-        <v>11.39452596925435</v>
+        <v>1.61210720552757</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[413.03, 403.65, 451.51]</t>
+          <t>[796.84, 368.92, 406.83]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[477.49, 472.46, 500.77]</t>
+          <t>[795.3, 373.6, 415.8]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>61.41755353288594</v>
+        <v>5.90908928982338</v>
       </c>
       <c r="G169" t="n">
-        <v>60.84288300456834</v>
+        <v>5.064201695717543</v>
       </c>
       <c r="H169" t="n">
-        <v>12.63351484672169</v>
+        <v>1.20135318854246</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[409.95, 458.39, 1386.45]</t>
+          <t>[368.66, 406.55, 1523.95]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[472.46, 500.77, 1445.38]</t>
+          <t>[373.6, 415.8, 1513.7]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>55.3066103294138</v>
+        <v>8.466629160477099</v>
       </c>
       <c r="G170" t="n">
-        <v>54.60693832821878</v>
+        <v>8.146950827372867</v>
       </c>
       <c r="H170" t="n">
-        <v>8.590312628051461</v>
+        <v>1.407945601332194</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[464.31, 1403.58, 1959.73]</t>
+          <t>[408.6, 1531.14, 640.14]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[500.77, 1445.38, 1960.9]</t>
+          <t>[415.8, 1513.7, 751.7]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>32.02988768358806</v>
+        <v>65.32400394175839</v>
       </c>
       <c r="G171" t="n">
-        <v>26.47649187509959</v>
+        <v>45.39993345846487</v>
       </c>
       <c r="H171" t="n">
-        <v>3.410632222444131</v>
+        <v>5.908383256548683</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[1412.71, 1972.45, 2427.88]</t>
+          <t>[3250.35, 3623.54, 3594.81]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[1445.38, 1960.9, 2428.74]</t>
+          <t>[2132.52, 2747.67, 2928.02]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>20.00991035661654</v>
+        <v>905.7777735790343</v>
       </c>
       <c r="G172" t="n">
-        <v>15.02670239066674</v>
+        <v>886.8295966249128</v>
       </c>
       <c r="H172" t="n">
-        <v>0.9615369416460323</v>
+        <v>35.68926375702126</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[1976.79, 2433.3, 2030.27]</t>
+          <t>[4231.3, 2951.63, 2388.38]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[1960.9, 2428.74, 2033.61]</t>
+          <t>[2747.67, 2928.02, 2811.94]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>9.73866362070701</v>
+        <v>890.9029254427408</v>
       </c>
       <c r="G173" t="n">
-        <v>7.932653948733787</v>
+        <v>643.5992012242788</v>
       </c>
       <c r="H173" t="n">
-        <v>0.387569322085855</v>
+        <v>23.28837023262556</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[2431.29, 2028.52, 849.8]</t>
+          <t>[2767.6, 2444.51, 3609.17]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[2428.74, 2033.61, 833.88]</t>
+          <t>[2928.02, 2811.94, 4615.15]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>9.759342819184184</v>
+        <v>625.2311399327153</v>
       </c>
       <c r="G174" t="n">
-        <v>7.852283749067965</v>
+        <v>511.2771081497804</v>
       </c>
       <c r="H174" t="n">
-        <v>0.7546704829247426</v>
+        <v>13.44763587094351</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[2028.3, 849.7, 1111.07]</t>
+          <t>[2460.44, 3631.22, 1768.24]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[2033.61, 833.88, 1068.47]</t>
+          <t>[2811.94, 4615.15, 1631.78]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>26.4136062893106</v>
+        <v>608.3577449254282</v>
       </c>
       <c r="G175" t="n">
-        <v>21.24273294251664</v>
+        <v>490.6298213339742</v>
       </c>
       <c r="H175" t="n">
-        <v>2.048372873971053</v>
+        <v>14.06077470716427</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[849.94, 1111.38, 1564.67]</t>
+          <t>[3747.14, 1850.51, 1616.88]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[833.88, 1068.47, 1523.63]</t>
+          <t>[4615.15, 1631.78, 1565.58]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>35.5157559381484</v>
+        <v>517.662546723617</v>
       </c>
       <c r="G176" t="n">
-        <v>33.33975912521434</v>
+        <v>379.3497236814701</v>
       </c>
       <c r="H176" t="n">
-        <v>2.878802744534816</v>
+        <v>11.8297975472323</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[2825.98, 3207.64, 3442.4]</t>
+          <t>[2038.9, 1694.63, 1599.49]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[2303.08, 2285.14, 2455.58]</t>
+          <t>[1631.78, 1565.58, 1804.74]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>836.3099949712063</v>
+        <v>273.5766336038074</v>
       </c>
       <c r="G177" t="n">
-        <v>810.74015862128</v>
+        <v>247.1423963097589</v>
       </c>
       <c r="H177" t="n">
-        <v>34.42025661076868</v>
+        <v>14.85521544091677</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[2872.42, 3088.27, 2671.83]</t>
+          <t>[1622.63, 1522.57, 2045.49]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[2285.14, 2455.58, 2078.31]</t>
+          <t>[1565.58, 1804.74, 1533.22]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>604.8317045274717</v>
+        <v>339.2620417855782</v>
       </c>
       <c r="G178" t="n">
-        <v>604.4976256910762</v>
+        <v>283.8316912109281</v>
       </c>
       <c r="H178" t="n">
-        <v>26.67442765890213</v>
+        <v>17.56354688116581</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[2652.2, 2301.22, 1639.17]</t>
+          <t>[1515.01, 2036.16, 1989.3]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[2455.58, 2078.31, 1836.76]</t>
+          <t>[1804.74, 1533.22, 1589.3]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>206.0676570506995</v>
+        <v>406.9784917319988</v>
       </c>
       <c r="G179" t="n">
-        <v>205.7080220842379</v>
+        <v>397.5581362860887</v>
       </c>
       <c r="H179" t="n">
-        <v>9.830108679848342</v>
+        <v>24.67508646426225</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[2180.53, 1554.91, 2358.0]</t>
+          <t>[2080.94, 2025.06, 4168.29]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[2078.31, 1836.76, 2246.84]</t>
+          <t>[1533.22, 1589.3, 3332.59]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>184.6153461012688</v>
+        <v>629.360878041012</v>
       </c>
       <c r="G180" t="n">
-        <v>165.0796924704206</v>
+        <v>606.3951127856732</v>
       </c>
       <c r="H180" t="n">
-        <v>8.403742287674904</v>
+        <v>29.40623422817311</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[1504.55, 2281.51, 2073.48]</t>
+          <t>[1938.98, 3972.63, 2141.53]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[1836.76, 2246.84, 2091.29]</t>
+          <t>[1589.3, 3332.59, 2325.81]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>193.1143332426129</v>
+        <v>434.3122085084876</v>
       </c>
       <c r="G181" t="n">
-        <v>128.2272284870108</v>
+        <v>391.3303636602034</v>
       </c>
       <c r="H181" t="n">
-        <v>6.826999597145038</v>
+        <v>16.37680966571616</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[2602.05, 2359.82, 2036.06]</t>
+          <t>[2431.29, 2028.52, 849.8]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[2246.84, 2091.29, 1955.9]</t>
+          <t>[2428.74, 2033.61, 833.88]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>261.2229431096616</v>
+        <v>9.759342819184184</v>
       </c>
       <c r="G182" t="n">
-        <v>234.6345788385514</v>
+        <v>7.852283749067965</v>
       </c>
       <c r="H182" t="n">
-        <v>10.91607815198034</v>
+        <v>0.7546704829247426</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[2147.41, 1855.44, 2352.38]</t>
+          <t>[2028.3, 849.7, 1111.07]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[2091.29, 1955.9, 3893.88]</t>
+          <t>[2033.61, 833.88, 1068.47]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>892.4628296025103</v>
+        <v>26.4136062893106</v>
       </c>
       <c r="G183" t="n">
-        <v>566.0262489085854</v>
+        <v>21.24273294251664</v>
       </c>
       <c r="H183" t="n">
-        <v>15.80247194088128</v>
+        <v>2.048372873971053</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[1823.99, 2313.67, 3097.32]</t>
+          <t>[849.94, 1111.38, 1564.67]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[1955.9, 3893.88, 4357.98]</t>
+          <t>[833.88, 1068.47, 1523.63]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1169.577698581424</v>
+        <v>35.5157559381484</v>
       </c>
       <c r="G184" t="n">
-        <v>990.9276034499635</v>
+        <v>33.33975912521434</v>
       </c>
       <c r="H184" t="n">
-        <v>25.41792002934677</v>
+        <v>2.878802744534816</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[2417.39, 3234.31, 4083.19]</t>
+          <t>[1109.12, 1561.5, 1001.53]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[3893.88, 4357.98, 5998.64]</t>
+          <t>[1068.47, 1523.63, 1080.05]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1539.654964118643</v>
+        <v>55.53105196509807</v>
       </c>
       <c r="G185" t="n">
-        <v>1505.204288105165</v>
+        <v>52.34439584420746</v>
       </c>
       <c r="H185" t="n">
-        <v>31.87795617361668</v>
+        <v>4.519796001862812</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[1555.74, 997.99, 295.06]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[1523.63, 1080.05, 307.15]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>51.35336210450495</v>
+      </c>
+      <c r="G186" t="n">
+        <v>42.08861673227106</v>
+      </c>
+      <c r="H186" t="n">
+        <v>4.547324203803749</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[996.13, 294.5, 483.92]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[1080.05, 307.15, 569.05]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>69.40106232060096</v>
+      </c>
+      <c r="G187" t="n">
+        <v>60.56674435836012</v>
+      </c>
+      <c r="H187" t="n">
+        <v>8.949500237785429</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[296.61, 487.24, 476.42]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[307.15, 569.05, 522.74]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>54.61968603902659</v>
+      </c>
+      <c r="G188" t="n">
+        <v>46.22508561930994</v>
+      </c>
+      <c r="H188" t="n">
+        <v>8.890083460478021</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[488.72, 477.78, 503.14]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[569.05, 522.74, 506.27]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>53.17835307295697</v>
+      </c>
+      <c r="G189" t="n">
+        <v>42.80799558110863</v>
+      </c>
+      <c r="H189" t="n">
+        <v>7.778816005936302</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[484.09, 509.72, 1468.29]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[522.74, 506.27, 1524.19]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>39.28932966255543</v>
+      </c>
+      <c r="G190" t="n">
+        <v>32.6693405951991</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3.914633840641862</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[513.16, 1478.18, 2006.85]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[506.27, 1524.19, 2030.74]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>30.19754304339066</v>
+      </c>
+      <c r="G191" t="n">
+        <v>25.60029394083388</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1.852361130068737</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[1823.99, 2313.67, 3097.32]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[1955.9, 3893.88, 4357.98]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1169.577698581424</v>
+      </c>
+      <c r="G192" t="n">
+        <v>990.9276034499635</v>
+      </c>
+      <c r="H192" t="n">
+        <v>25.41792002934677</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[2417.39, 3234.31, 4083.19]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[3893.88, 4357.98, 5998.64]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1539.654964118643</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1505.204288105165</v>
+      </c>
+      <c r="H193" t="n">
+        <v>31.87795617361668</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[4448.77, 5593.19, 6590.43]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[4357.98, 5998.64, 8733.53]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>1260.360363029279</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>879.7809938981842</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>11.12704239017476</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[5507.3, 6489.91, 2863.9]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[5998.64, 8733.53, 2598.76]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1334.862212162786</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1000.037278183948</v>
+      </c>
+      <c r="H195" t="n">
+        <v>14.69445661206452</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[6875.91, 3032.3, 3365.45]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[8733.53, 2598.76, 2732.23]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1160.413115347824</v>
+      </c>
+      <c r="G196" t="n">
+        <v>974.7936243487115</v>
+      </c>
+      <c r="H196" t="n">
+        <v>20.37617814618192</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[3585.02, 3970.47, 4253.01]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[2598.76, 2732.23, 2726.66]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1269.606752844358</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1250.285028077313</v>
+      </c>
+      <c r="H197" t="n">
+        <v>46.41662361775574</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[3227.68, 3465.65, 2983.61]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[2732.23, 2726.66, 2579.69]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>564.1261769488871</v>
+      </c>
+      <c r="G198" t="n">
+        <v>546.1161862878699</v>
+      </c>
+      <c r="H198" t="n">
+        <v>20.29773350512857</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[3107.2, 2679.17, 1974.26]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[2726.66, 2579.69, 1902.11]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>230.8776801664053</v>
+      </c>
+      <c r="G199" t="n">
+        <v>184.0556497996298</v>
+      </c>
+      <c r="H199" t="n">
+        <v>7.201853904829138</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[2449.93, 1807.7, 2641.67]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[2579.69, 1902.11, 2208.35]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>266.7820036629229</v>
+      </c>
+      <c r="G200" t="n">
+        <v>219.1640722493726</v>
+      </c>
+      <c r="H200" t="n">
+        <v>9.871814646860045</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[1871.39, 2734.46, 2487.62]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[1902.11, 2208.35, 2272.74]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>328.5877313270672</v>
+      </c>
+      <c r="G201" t="n">
+        <v>257.2352705352084</v>
+      </c>
+      <c r="H201" t="n">
+        <v>11.63105750272325</v>
       </c>
     </row>
   </sheetData>
